--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77CFD4A8-2BEF-4469-9F6F-82EB672F069C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5E82F4B-2BA7-4230-804D-35CA3B1A17AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="481">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -849,16 +849,52 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_solelc_spv_004</t>
@@ -867,6 +903,42 @@
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_014</t>
   </si>
   <si>
@@ -897,133 +969,85 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem2,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem1,e_dem4,e_dem3,e_gen2</t>
+  </si>
+  <si>
+    <t>e_dem3,e_gen2</t>
+  </si>
+  <si>
     <t>e_dem0</t>
   </si>
   <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
     <t>e_gen3</t>
   </si>
   <si>
+    <t>e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen3,e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem2,e_gen3,e_dem0</t>
+  </si>
+  <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
     <t>e_gen1,e_dem1,e_dem3</t>
   </si>
   <si>
     <t>e_dem4,e_dem0</t>
   </si>
   <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
     <t>e_dem4,e_gen2</t>
   </si>
   <si>
-    <t>e_gen3,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem1,e_dem4,e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2</t>
-  </si>
-  <si>
     <t>e_dem2,e_gen3</t>
   </si>
   <si>
-    <t>e_dem2,e_gen3,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_014</t>
@@ -1044,16 +1068,10 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_005</t>
@@ -1062,22 +1080,40 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_016</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wonelc_won_009</t>
@@ -1104,46 +1140,34 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_004</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen4,e_dem4,e_gen2</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_dem0,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem4</t>
   </si>
   <si>
     <t>elc_won_014</t>
@@ -1158,31 +1182,37 @@
     <t>elc_won_015</t>
   </si>
   <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem4</t>
+    <t>elc_won_007</t>
   </si>
   <si>
     <t>elc_won_005</t>
   </si>
   <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_gen3,e_gen0,e_dem0</t>
+  </si>
+  <si>
     <t>elc_won_016</t>
   </si>
   <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen0,e_dem0</t>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem2</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
   </si>
   <si>
     <t>elc_won_009</t>
@@ -1197,39 +1227,9 @@
     <t>elc_won_018</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
     <t>elc_won_004</t>
   </si>
   <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem2</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen4,e_dem4,e_gen2</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_dem0,e_dem4</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
@@ -1242,16 +1242,40 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -1266,30 +1290,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
@@ -1299,28 +1299,28 @@
     <t>elc_wof_007</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>elc_wof_008</t>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
   </si>
   <si>
     <t>elc_wof_001</t>
   </si>
   <si>
     <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -1584,7 +1584,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1732,8 +1732,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1825,6 +1832,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2039,7 +2051,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2059,8 +2071,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2452,6 +2465,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2471,8 +2485,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -2865,423 +2880,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -3289,32 +2977,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -3322,37 +3010,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -3364,120 +3052,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5023,25 +5046,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5087,7 +5110,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5132,7 +5155,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5174,7 +5197,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6279,7 +6302,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D8EC0A6-D1F9-43D5-99DD-860C73FF57CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF485E7-94C5-4D13-98B7-6F397677E2A0}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6517,16 +6540,16 @@
         <v>240</v>
       </c>
       <c r="Y11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Z11" t="s">
         <v>284</v>
       </c>
       <c r="AA11">
-        <v>0.99536570131993762</v>
+        <v>0.98911580324852866</v>
       </c>
       <c r="AB11">
-        <v>84.962142467809898</v>
+        <v>199.54360711030768</v>
       </c>
       <c r="AD11" t="s">
         <v>239</v>
@@ -6556,13 +6579,13 @@
         <v>339</v>
       </c>
       <c r="AN11" t="s">
-        <v>295</v>
+        <v>340</v>
       </c>
       <c r="AO11">
-        <v>0.99368847580230268</v>
+        <v>0.99363378101904942</v>
       </c>
       <c r="AP11">
-        <v>115.71127695778416</v>
+        <v>116.71401465075998</v>
       </c>
       <c r="AR11" t="s">
         <v>239</v>
@@ -6663,16 +6686,16 @@
         <v>244</v>
       </c>
       <c r="Y12" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="Z12" t="s">
         <v>285</v>
       </c>
       <c r="AA12">
-        <v>0.99559401474611386</v>
+        <v>0.99315229827185159</v>
       </c>
       <c r="AB12">
-        <v>80.776396321244846</v>
+        <v>125.54119834938666</v>
       </c>
       <c r="AD12" t="s">
         <v>239</v>
@@ -6699,16 +6722,16 @@
         <v>301</v>
       </c>
       <c r="AM12" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO12">
-        <v>0.99582677011152854</v>
+        <v>0.98844945266915318</v>
       </c>
       <c r="AP12">
-        <v>76.509214621975957</v>
+        <v>211.76003439885758</v>
       </c>
       <c r="AR12" t="s">
         <v>239</v>
@@ -6738,7 +6761,7 @@
         <v>389</v>
       </c>
       <c r="BB12" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="BC12">
         <v>0.99207591869454059</v>
@@ -6809,16 +6832,16 @@
         <v>246</v>
       </c>
       <c r="Y13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Z13" t="s">
         <v>286</v>
       </c>
       <c r="AA13">
-        <v>0.99306360188977116</v>
+        <v>0.98883640519674998</v>
       </c>
       <c r="AB13">
-        <v>127.16729868752907</v>
+        <v>204.66590472624989</v>
       </c>
       <c r="AD13" t="s">
         <v>239</v>
@@ -6845,16 +6868,16 @@
         <v>303</v>
       </c>
       <c r="AM13" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AN13" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="AO13">
-        <v>0.9911442551729287</v>
+        <v>0.99427708421681416</v>
       </c>
       <c r="AP13">
-        <v>162.35532182964019</v>
+        <v>104.92012269174036</v>
       </c>
       <c r="AR13" t="s">
         <v>239</v>
@@ -6884,13 +6907,13 @@
         <v>390</v>
       </c>
       <c r="BB13" t="s">
-        <v>388</v>
+        <v>290</v>
       </c>
       <c r="BC13">
-        <v>0.99136264788907857</v>
+        <v>0.98926313025711288</v>
       </c>
       <c r="BD13">
-        <v>158.35145536689319</v>
+        <v>196.84261195293161</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6955,16 +6978,16 @@
         <v>248</v>
       </c>
       <c r="Y14" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Z14" t="s">
         <v>287</v>
       </c>
       <c r="AA14">
-        <v>0.990012010348303</v>
+        <v>0.99536570131993762</v>
       </c>
       <c r="AB14">
-        <v>183.11314361444599</v>
+        <v>84.962142467809898</v>
       </c>
       <c r="AD14" t="s">
         <v>239</v>
@@ -6991,16 +7014,16 @@
         <v>305</v>
       </c>
       <c r="AM14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AN14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AO14">
-        <v>0.99427708421681416</v>
+        <v>0.99392750374448113</v>
       </c>
       <c r="AP14">
-        <v>104.92012269174036</v>
+        <v>111.32909801784524</v>
       </c>
       <c r="AR14" t="s">
         <v>239</v>
@@ -7030,13 +7053,13 @@
         <v>391</v>
       </c>
       <c r="BB14" t="s">
-        <v>285</v>
+        <v>388</v>
       </c>
       <c r="BC14">
-        <v>0.98926313025711288</v>
+        <v>0.99136264788907857</v>
       </c>
       <c r="BD14">
-        <v>196.84261195293161</v>
+        <v>158.35145536689319</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7101,16 +7124,16 @@
         <v>250</v>
       </c>
       <c r="Y15" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="Z15" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AA15">
-        <v>0.98893381891519438</v>
+        <v>0.99356288436829876</v>
       </c>
       <c r="AB15">
-        <v>202.87998655476954</v>
+        <v>118.01378658118981</v>
       </c>
       <c r="AD15" t="s">
         <v>239</v>
@@ -7137,16 +7160,16 @@
         <v>307</v>
       </c>
       <c r="AM15" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AN15" t="s">
-        <v>346</v>
+        <v>293</v>
       </c>
       <c r="AO15">
-        <v>0.99392750374448113</v>
+        <v>0.99368847580230268</v>
       </c>
       <c r="AP15">
-        <v>111.32909801784524</v>
+        <v>115.71127695778416</v>
       </c>
       <c r="AR15" t="s">
         <v>239</v>
@@ -7176,13 +7199,13 @@
         <v>392</v>
       </c>
       <c r="BB15" t="s">
-        <v>284</v>
+        <v>388</v>
       </c>
       <c r="BC15">
-        <v>0.9941446088905187</v>
+        <v>0.99520217301523817</v>
       </c>
       <c r="BD15">
-        <v>107.34883700715665</v>
+        <v>87.960161387300914</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7247,16 +7270,16 @@
         <v>252</v>
       </c>
       <c r="Y16" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Z16" t="s">
         <v>288</v>
       </c>
       <c r="AA16">
-        <v>0.9866385672597856</v>
+        <v>0.99442875744459613</v>
       </c>
       <c r="AB16">
-        <v>244.95960023726295</v>
+        <v>102.13944684907001</v>
       </c>
       <c r="AD16" t="s">
         <v>239</v>
@@ -7283,16 +7306,16 @@
         <v>309</v>
       </c>
       <c r="AM16" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN16" t="s">
-        <v>289</v>
+        <v>349</v>
       </c>
       <c r="AO16">
-        <v>0.98751891498768063</v>
+        <v>0.99582677011152854</v>
       </c>
       <c r="AP16">
-        <v>228.81989189252232</v>
+        <v>76.509214621975957</v>
       </c>
       <c r="AR16" t="s">
         <v>239</v>
@@ -7322,13 +7345,13 @@
         <v>393</v>
       </c>
       <c r="BB16" t="s">
-        <v>284</v>
+        <v>388</v>
       </c>
       <c r="BC16">
-        <v>0.99204351007823377</v>
+        <v>0.99136108064447537</v>
       </c>
       <c r="BD16">
-        <v>145.8689818990471</v>
+        <v>158.38018818461751</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7393,16 +7416,16 @@
         <v>254</v>
       </c>
       <c r="Y17" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Z17" t="s">
         <v>289</v>
       </c>
       <c r="AA17">
-        <v>0.98928494645383225</v>
+        <v>0.99131060083308187</v>
       </c>
       <c r="AB17">
-        <v>196.44264834640867</v>
+        <v>159.30565139349844</v>
       </c>
       <c r="AD17" t="s">
         <v>239</v>
@@ -7429,16 +7452,16 @@
         <v>311</v>
       </c>
       <c r="AM17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AN17" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="AO17">
-        <v>0.99053113122064196</v>
+        <v>0.9911442551729287</v>
       </c>
       <c r="AP17">
-        <v>173.59592762156493</v>
+        <v>162.35532182964019</v>
       </c>
       <c r="AR17" t="s">
         <v>239</v>
@@ -7468,13 +7491,13 @@
         <v>394</v>
       </c>
       <c r="BB17" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="BC17">
-        <v>0.99520217301523817</v>
+        <v>0.98954715343009803</v>
       </c>
       <c r="BD17">
-        <v>87.960161387300914</v>
+        <v>191.63552044820315</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7539,16 +7562,16 @@
         <v>256</v>
       </c>
       <c r="Y18" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z18" t="s">
         <v>290</v>
       </c>
       <c r="AA18">
-        <v>0.99371757160137486</v>
+        <v>0.99559401474611386</v>
       </c>
       <c r="AB18">
-        <v>115.17785397479503</v>
+        <v>80.776396321244846</v>
       </c>
       <c r="AD18" t="s">
         <v>239</v>
@@ -7575,16 +7598,16 @@
         <v>313</v>
       </c>
       <c r="AM18" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AN18" t="s">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="AO18">
-        <v>0.98768981100926756</v>
+        <v>0.99353102787032765</v>
       </c>
       <c r="AP18">
-        <v>225.68679816342777</v>
+        <v>118.59782237732686</v>
       </c>
       <c r="AR18" t="s">
         <v>239</v>
@@ -7617,10 +7640,10 @@
         <v>388</v>
       </c>
       <c r="BC18">
-        <v>0.99136108064447537</v>
+        <v>0.99333526531977001</v>
       </c>
       <c r="BD18">
-        <v>158.38018818461751</v>
+        <v>122.18680247088278</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7685,16 +7708,16 @@
         <v>258</v>
       </c>
       <c r="Y19" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="Z19" t="s">
         <v>291</v>
       </c>
       <c r="AA19">
-        <v>0.98911580324852866</v>
+        <v>0.99589633147839685</v>
       </c>
       <c r="AB19">
-        <v>199.54360711030768</v>
+        <v>75.233922896057891</v>
       </c>
       <c r="AD19" t="s">
         <v>239</v>
@@ -7721,16 +7744,16 @@
         <v>315</v>
       </c>
       <c r="AM19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AN19" t="s">
-        <v>351</v>
+        <v>297</v>
       </c>
       <c r="AO19">
-        <v>0.99419279872301636</v>
+        <v>0.98751891498768063</v>
       </c>
       <c r="AP19">
-        <v>106.46535674469997</v>
+        <v>228.81989189252232</v>
       </c>
       <c r="AR19" t="s">
         <v>239</v>
@@ -7760,13 +7783,13 @@
         <v>396</v>
       </c>
       <c r="BB19" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="BC19">
-        <v>0.98954715343009803</v>
+        <v>0.9941446088905187</v>
       </c>
       <c r="BD19">
-        <v>191.63552044820315</v>
+        <v>107.34883700715665</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7831,16 +7854,16 @@
         <v>260</v>
       </c>
       <c r="Y20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Z20" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AA20">
-        <v>0.99315229827185159</v>
+        <v>0.9962937079492431</v>
       </c>
       <c r="AB20">
-        <v>125.54119834938666</v>
+        <v>67.94868759721048</v>
       </c>
       <c r="AD20" t="s">
         <v>239</v>
@@ -7867,16 +7890,16 @@
         <v>317</v>
       </c>
       <c r="AM20" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN20" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="AO20">
-        <v>0.99552303355529737</v>
+        <v>0.98768981100926756</v>
       </c>
       <c r="AP20">
-        <v>82.077718152882312</v>
+        <v>225.68679816342777</v>
       </c>
       <c r="AR20" t="s">
         <v>239</v>
@@ -7906,13 +7929,13 @@
         <v>397</v>
       </c>
       <c r="BB20" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="BC20">
-        <v>0.99333526531977001</v>
+        <v>0.99204351007823377</v>
       </c>
       <c r="BD20">
-        <v>122.18680247088278</v>
+        <v>145.8689818990471</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7977,16 +8000,16 @@
         <v>262</v>
       </c>
       <c r="Y21" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z21" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AA21">
-        <v>0.98883640519674998</v>
+        <v>0.99371757160137486</v>
       </c>
       <c r="AB21">
-        <v>204.66590472624989</v>
+        <v>115.17785397479503</v>
       </c>
       <c r="AD21" t="s">
         <v>239</v>
@@ -8013,16 +8036,16 @@
         <v>319</v>
       </c>
       <c r="AM21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AN21" t="s">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="AO21">
-        <v>0.9913766042890243</v>
+        <v>0.99419279872301636</v>
       </c>
       <c r="AP21">
-        <v>158.09558803455363</v>
+        <v>106.46535674469997</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8087,16 +8110,16 @@
         <v>264</v>
       </c>
       <c r="Y22" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Z22" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AA22">
-        <v>0.9905299918588647</v>
+        <v>0.99372835533859694</v>
       </c>
       <c r="AB22">
-        <v>173.61681592081291</v>
+        <v>114.98015212572193</v>
       </c>
       <c r="AD22" t="s">
         <v>239</v>
@@ -8123,16 +8146,16 @@
         <v>321</v>
       </c>
       <c r="AM22" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AN22" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AO22">
-        <v>0.99498199124719422</v>
+        <v>0.99053113122064196</v>
       </c>
       <c r="AP22">
-        <v>91.99682713477273</v>
+        <v>173.59592762156493</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8197,16 +8220,16 @@
         <v>266</v>
       </c>
       <c r="Y23" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="AA23">
-        <v>0.99372835533859694</v>
+        <v>0.9964587744572686</v>
       </c>
       <c r="AB23">
-        <v>114.98015212572193</v>
+        <v>64.922468283408804</v>
       </c>
       <c r="AD23" t="s">
         <v>239</v>
@@ -8233,16 +8256,16 @@
         <v>323</v>
       </c>
       <c r="AM23" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AN23" t="s">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="AO23">
-        <v>0.98926286248458195</v>
+        <v>0.99436493305946672</v>
       </c>
       <c r="AP23">
-        <v>196.84752111599829</v>
+        <v>103.30956057644399</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8307,16 +8330,16 @@
         <v>268</v>
       </c>
       <c r="Y24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z24" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AA24">
-        <v>0.9964587744572686</v>
+        <v>0.99630851076955973</v>
       </c>
       <c r="AB24">
-        <v>64.922468283408804</v>
+        <v>67.677302558071602</v>
       </c>
       <c r="AD24" t="s">
         <v>239</v>
@@ -8343,16 +8366,16 @@
         <v>325</v>
       </c>
       <c r="AM24" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN24" t="s">
         <v>288</v>
       </c>
       <c r="AO24">
-        <v>0.99353102787032765</v>
+        <v>0.99558761976621801</v>
       </c>
       <c r="AP24">
-        <v>118.59782237732686</v>
+        <v>80.893637619336488</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8417,16 +8440,16 @@
         <v>270</v>
       </c>
       <c r="Y25" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="Z25" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="AA25">
-        <v>0.99630851076955973</v>
+        <v>0.99306360188977116</v>
       </c>
       <c r="AB25">
-        <v>67.677302558071602</v>
+        <v>127.16729868752907</v>
       </c>
       <c r="AD25" t="s">
         <v>239</v>
@@ -8453,16 +8476,16 @@
         <v>327</v>
       </c>
       <c r="AM25" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AN25" t="s">
-        <v>296</v>
+        <v>361</v>
       </c>
       <c r="AO25">
-        <v>0.99558761976621801</v>
+        <v>0.99520787559028878</v>
       </c>
       <c r="AP25">
-        <v>80.893637619336488</v>
+        <v>87.85561417803892</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8527,16 +8550,16 @@
         <v>272</v>
       </c>
       <c r="Y26" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Z26" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="AA26">
-        <v>0.99356288436829876</v>
+        <v>0.990012010348303</v>
       </c>
       <c r="AB26">
-        <v>118.01378658118981</v>
+        <v>183.11314361444599</v>
       </c>
       <c r="AD26" t="s">
         <v>239</v>
@@ -8563,16 +8586,16 @@
         <v>329</v>
       </c>
       <c r="AM26" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="AN26" t="s">
-        <v>359</v>
+        <v>287</v>
       </c>
       <c r="AO26">
-        <v>0.99520787559028878</v>
+        <v>0.99552303355529737</v>
       </c>
       <c r="AP26">
-        <v>87.85561417803892</v>
+        <v>82.077718152882312</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8637,16 +8660,16 @@
         <v>274</v>
       </c>
       <c r="Y27" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="Z27" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="AA27">
-        <v>0.99442875744459613</v>
+        <v>0.98893381891519438</v>
       </c>
       <c r="AB27">
-        <v>102.13944684907001</v>
+        <v>202.87998655476954</v>
       </c>
       <c r="AD27" t="s">
         <v>239</v>
@@ -8673,16 +8696,16 @@
         <v>331</v>
       </c>
       <c r="AM27" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AN27" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="AO27">
-        <v>0.98909696821272286</v>
+        <v>0.9913766042890243</v>
       </c>
       <c r="AP27">
-        <v>199.88891610008122</v>
+        <v>158.09558803455363</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -8747,16 +8770,16 @@
         <v>276</v>
       </c>
       <c r="Y28" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Z28" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AA28">
-        <v>0.99131060083308187</v>
+        <v>0.9866385672597856</v>
       </c>
       <c r="AB28">
-        <v>159.30565139349844</v>
+        <v>244.95960023726295</v>
       </c>
       <c r="AD28" t="s">
         <v>239</v>
@@ -8783,16 +8806,16 @@
         <v>333</v>
       </c>
       <c r="AM28" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AN28" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="AO28">
-        <v>0.99436493305946672</v>
+        <v>0.99498199124719422</v>
       </c>
       <c r="AP28">
-        <v>103.30956057644399</v>
+        <v>91.99682713477273</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8857,16 +8880,16 @@
         <v>278</v>
       </c>
       <c r="Y29" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="Z29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA29">
-        <v>0.99589633147839685</v>
+        <v>0.98928494645383225</v>
       </c>
       <c r="AB29">
-        <v>75.233922896057891</v>
+        <v>196.44264834640867</v>
       </c>
       <c r="AD29" t="s">
         <v>239</v>
@@ -8893,16 +8916,16 @@
         <v>335</v>
       </c>
       <c r="AM29" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AN29" t="s">
-        <v>364</v>
+        <v>284</v>
       </c>
       <c r="AO29">
-        <v>0.99363378101904942</v>
+        <v>0.98926286248458195</v>
       </c>
       <c r="AP29">
-        <v>116.71401465075998</v>
+        <v>196.84752111599829</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8967,16 +8990,16 @@
         <v>280</v>
       </c>
       <c r="Y30" t="s">
-        <v>237</v>
+        <v>218</v>
       </c>
       <c r="Z30" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AA30">
-        <v>0.9962937079492431</v>
+        <v>0.9905299918588647</v>
       </c>
       <c r="AB30">
-        <v>67.94868759721048</v>
+        <v>173.61681592081291</v>
       </c>
       <c r="AD30" t="s">
         <v>239</v>
@@ -9003,16 +9026,16 @@
         <v>337</v>
       </c>
       <c r="AM30" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN30" t="s">
-        <v>366</v>
+        <v>289</v>
       </c>
       <c r="AO30">
-        <v>0.98844945266915318</v>
+        <v>0.98909696821272286</v>
       </c>
       <c r="AP30">
-        <v>211.76003439885758</v>
+        <v>199.88891610008122</v>
       </c>
     </row>
   </sheetData>
@@ -9021,7 +9044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{488FA87F-4FEB-45EC-BC3E-FE9245DFFB20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C42831-07FE-4634-97C7-7A0755AD8A77}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9133,7 +9156,7 @@
         <v>398</v>
       </c>
       <c r="K11" t="s">
-        <v>363</v>
+        <v>339</v>
       </c>
       <c r="L11">
         <v>0.45167200935612223</v>
@@ -9166,7 +9189,7 @@
         <v>438</v>
       </c>
       <c r="X11" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -9201,7 +9224,7 @@
         <v>400</v>
       </c>
       <c r="K12" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="L12">
         <v>0.50504353376491207</v>
@@ -9234,7 +9257,7 @@
         <v>440</v>
       </c>
       <c r="X12" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -9302,7 +9325,7 @@
         <v>442</v>
       </c>
       <c r="X13" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -9337,7 +9360,7 @@
         <v>404</v>
       </c>
       <c r="K14" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="L14">
         <v>2.6804732670444085</v>
@@ -9370,7 +9393,7 @@
         <v>444</v>
       </c>
       <c r="X14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9405,7 +9428,7 @@
         <v>406</v>
       </c>
       <c r="K15" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="L15">
         <v>8.0517810049421517</v>
@@ -9438,7 +9461,7 @@
         <v>446</v>
       </c>
       <c r="X15" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9473,7 +9496,7 @@
         <v>408</v>
       </c>
       <c r="K16" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L16">
         <v>0.96273897344398884</v>
@@ -9541,7 +9564,7 @@
         <v>410</v>
       </c>
       <c r="K17" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="L17">
         <v>1.093890418371007</v>
@@ -9609,7 +9632,7 @@
         <v>412</v>
       </c>
       <c r="K18" t="s">
-        <v>365</v>
+        <v>341</v>
       </c>
       <c r="L18">
         <v>3.1665724666245323</v>
@@ -9642,7 +9665,7 @@
         <v>452</v>
       </c>
       <c r="X18" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9677,7 +9700,7 @@
         <v>414</v>
       </c>
       <c r="K19" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="L19">
         <v>0.55491188155257321</v>
@@ -9710,7 +9733,7 @@
         <v>454</v>
       </c>
       <c r="X19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9745,7 +9768,7 @@
         <v>416</v>
       </c>
       <c r="K20" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L20">
         <v>0.97886072674627833</v>
@@ -9778,7 +9801,7 @@
         <v>456</v>
       </c>
       <c r="X20" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9813,7 +9836,7 @@
         <v>418</v>
       </c>
       <c r="K21" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L21">
         <v>0.40593208719379742</v>
@@ -9848,7 +9871,7 @@
         <v>420</v>
       </c>
       <c r="K22" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="L22">
         <v>0.8833561507867439</v>
@@ -9918,7 +9941,7 @@
         <v>424</v>
       </c>
       <c r="K24" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="L24">
         <v>0.84020182400735144</v>
@@ -9953,7 +9976,7 @@
         <v>426</v>
       </c>
       <c r="K25" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -9988,7 +10011,7 @@
         <v>428</v>
       </c>
       <c r="K26" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="L26">
         <v>0.89446396558783758</v>
@@ -10023,7 +10046,7 @@
         <v>430</v>
       </c>
       <c r="K27" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10058,7 +10081,7 @@
         <v>432</v>
       </c>
       <c r="K28" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L28">
         <v>1.4637274230737423</v>
@@ -10093,7 +10116,7 @@
         <v>434</v>
       </c>
       <c r="K29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L29">
         <v>0.63042801517356961</v>
@@ -10128,7 +10151,7 @@
         <v>436</v>
       </c>
       <c r="K30" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="L30">
         <v>0.61343702722931326</v>
@@ -10143,7 +10166,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C72ED27-5806-4D14-8CE0-A98F7D26A61E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3B521F-A299-4E3E-A0D7-74FB2DA968BA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5E82F4B-2BA7-4230-804D-35CA3B1A17AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C5FB88-1554-4033-9793-9624D35A2E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="482">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1570,6 +1570,9 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>e_gen3,e_gen1</t>
   </si>
 </sst>
 </file>
@@ -3463,7 +3466,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_gen3,e_gen1</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3485,7 +3488,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_gen3,e_gen1</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3500,7 +3503,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>19</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C5FB88-1554-4033-9793-9624D35A2E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4AA5AC-9C6A-4AAB-BC11-B408A53BD035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="483">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1573,6 +1573,9 @@
   </si>
   <si>
     <t>e_gen3,e_gen1</t>
+  </si>
+  <si>
+    <t>AF</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2079,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2487,6 +2490,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -2966,6 +2970,9 @@
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
+      <c r="T12" s="154" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -3479,6 +3486,9 @@
       </c>
       <c r="S27">
         <v>50</v>
+      </c>
+      <c r="T27">
+        <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="2:22">

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A4AA5AC-9C6A-4AAB-BC11-B408A53BD035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8823A40-15BE-4AFD-90BF-0D28E59F915F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="485">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1576,6 +1576,12 @@
   </si>
   <si>
     <t>AF</t>
+  </si>
+  <si>
+    <t>Deact fi_process</t>
+  </si>
+  <si>
+    <t>Deact fi_t</t>
   </si>
 </sst>
 </file>
@@ -2472,6 +2478,7 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2490,7 +2497,6 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
@@ -2970,7 +2976,7 @@
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="154" t="s">
+      <c r="T12" s="148" t="s">
         <v>482</v>
       </c>
     </row>
@@ -5059,25 +5065,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="149" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
+      <c r="F1" s="150" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="149"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="149" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="149"/>
+      <c r="K1" s="149"/>
+      <c r="L1" s="149"/>
+      <c r="M1" s="149"/>
+      <c r="N1" s="149"/>
+      <c r="O1" s="152" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5123,7 +5129,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="153"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5168,7 +5174,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="153"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5210,7 +5216,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="154"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6327,22 +6333,22 @@
         <v>214</v>
       </c>
       <c r="O9" t="s">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="X9" t="s">
-        <v>214</v>
+        <v>484</v>
       </c>
       <c r="AD9" t="s">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="AL9" t="s">
-        <v>214</v>
+        <v>484</v>
       </c>
       <c r="AR9" t="s">
-        <v>163</v>
+        <v>483</v>
       </c>
       <c r="AZ9" t="s">
-        <v>214</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" spans="2:56">

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8823A40-15BE-4AFD-90BF-0D28E59F915F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017B7459-A9A6-40CB-A8A5-5EE8621F4FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="459">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -981,51 +981,6 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_dem2,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem1,e_dem4,e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen3,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1,e_dem3</t>
-  </si>
-  <si>
-    <t>e_dem4,e_dem0</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem2,e_gen3</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_001</t>
   </si>
   <si>
@@ -1149,36 +1104,21 @@
     <t>elc_won_001</t>
   </si>
   <si>
-    <t>e_dem1,e_gen4,e_dem4,e_gen2</t>
-  </si>
-  <si>
     <t>elc_won_008</t>
   </si>
   <si>
-    <t>e_dem0,e_dem4</t>
-  </si>
-  <si>
     <t>elc_won_013</t>
   </si>
   <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
     <t>elc_won_003</t>
   </si>
   <si>
-    <t>e_gen2,e_dem4</t>
-  </si>
-  <si>
     <t>elc_won_014</t>
   </si>
   <si>
     <t>elc_won_020</t>
   </si>
   <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
     <t>elc_won_015</t>
   </si>
   <si>
@@ -1194,27 +1134,18 @@
     <t>elc_won_010</t>
   </si>
   <si>
-    <t>e_gen3,e_gen0,e_dem0</t>
-  </si>
-  <si>
     <t>elc_won_016</t>
   </si>
   <si>
     <t>elc_won_012</t>
   </si>
   <si>
-    <t>e_gen3,e_dem2</t>
-  </si>
-  <si>
     <t>elc_won_006</t>
   </si>
   <si>
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
     <t>elc_won_009</t>
   </si>
   <si>
@@ -1293,9 +1224,6 @@
     <t>elc_wof_006</t>
   </si>
   <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
@@ -1576,12 +1504,6 @@
   </si>
   <si>
     <t>AF</t>
-  </si>
-  <si>
-    <t>Deact fi_process</t>
-  </si>
-  <si>
-    <t>Deact fi_t</t>
   </si>
 </sst>
 </file>
@@ -2977,7 +2899,7 @@
         <v>105</v>
       </c>
       <c r="T12" s="148" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
     </row>
     <row r="13" spans="2:22">
@@ -3519,7 +3441,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -6324,6 +6246,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF485E7-94C5-4D13-98B7-6F397677E2A0}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="25" max="25" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.19921875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="10.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
@@ -6333,22 +6260,22 @@
         <v>214</v>
       </c>
       <c r="O9" t="s">
-        <v>483</v>
+        <v>163</v>
       </c>
       <c r="X9" t="s">
-        <v>484</v>
+        <v>214</v>
       </c>
       <c r="AD9" t="s">
-        <v>483</v>
+        <v>163</v>
       </c>
       <c r="AL9" t="s">
-        <v>484</v>
+        <v>214</v>
       </c>
       <c r="AR9" t="s">
-        <v>483</v>
+        <v>163</v>
       </c>
       <c r="AZ9" t="s">
-        <v>484</v>
+        <v>214</v>
       </c>
     </row>
     <row r="10" spans="2:56">
@@ -6561,8 +6488,9 @@
       <c r="Y11" t="s">
         <v>219</v>
       </c>
-      <c r="Z11" t="s">
-        <v>284</v>
+      <c r="Z11" t="str">
+        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y11,2),0,"")</f>
+        <v>e_sol2</v>
       </c>
       <c r="AA11">
         <v>0.98911580324852866</v>
@@ -6574,10 +6502,10 @@
         <v>239</v>
       </c>
       <c r="AE11" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="AF11" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6592,13 +6520,14 @@
         <v>175</v>
       </c>
       <c r="AL11" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="AM11" t="s">
-        <v>339</v>
-      </c>
-      <c r="AN11" t="s">
-        <v>340</v>
+        <v>324</v>
+      </c>
+      <c r="AN11" t="str">
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM11,2),0,"")</f>
+        <v>e_won1</v>
       </c>
       <c r="AO11">
         <v>0.99363378101904942</v>
@@ -6610,10 +6539,10 @@
         <v>239</v>
       </c>
       <c r="AS11" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="AT11" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6628,13 +6557,14 @@
         <v>175</v>
       </c>
       <c r="AZ11" t="s">
-        <v>367</v>
+        <v>344</v>
       </c>
       <c r="BA11" t="s">
-        <v>387</v>
-      </c>
-      <c r="BB11" t="s">
-        <v>388</v>
+        <v>364</v>
+      </c>
+      <c r="BB11" t="str">
+        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA11,2),0,"")</f>
+        <v>e_wof6</v>
       </c>
       <c r="BC11">
         <v>0.99653064315884643</v>
@@ -6707,8 +6637,9 @@
       <c r="Y12" t="s">
         <v>236</v>
       </c>
-      <c r="Z12" t="s">
-        <v>285</v>
+      <c r="Z12" t="str">
+        <f t="shared" ref="Z12:Z30" si="0">"e_sol"&amp;SUBSTITUTE(RIGHT(Y12,2),0,"")</f>
+        <v>e_sol19</v>
       </c>
       <c r="AA12">
         <v>0.99315229827185159</v>
@@ -6720,10 +6651,10 @@
         <v>239</v>
       </c>
       <c r="AE12" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="AF12" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6738,13 +6669,14 @@
         <v>175</v>
       </c>
       <c r="AL12" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="AM12" t="s">
-        <v>341</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>342</v>
+        <v>325</v>
+      </c>
+      <c r="AN12" t="str">
+        <f t="shared" ref="AN12:AN30" si="1">"e_won"&amp;SUBSTITUTE(RIGHT(AM12,2),0,"")</f>
+        <v>e_won8</v>
       </c>
       <c r="AO12">
         <v>0.98844945266915318</v>
@@ -6756,10 +6688,10 @@
         <v>239</v>
       </c>
       <c r="AS12" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="AT12" t="s">
-        <v>370</v>
+        <v>347</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6774,13 +6706,14 @@
         <v>175</v>
       </c>
       <c r="AZ12" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="BA12" t="s">
-        <v>389</v>
-      </c>
-      <c r="BB12" t="s">
-        <v>290</v>
+        <v>365</v>
+      </c>
+      <c r="BB12" t="str">
+        <f t="shared" ref="BB12:BB20" si="2">"e_wof"&amp;SUBSTITUTE(RIGHT(BA12,2),0,"")</f>
+        <v>e_wof7</v>
       </c>
       <c r="BC12">
         <v>0.99207591869454059</v>
@@ -6853,8 +6786,9 @@
       <c r="Y13" t="s">
         <v>230</v>
       </c>
-      <c r="Z13" t="s">
-        <v>286</v>
+      <c r="Z13" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol13</v>
       </c>
       <c r="AA13">
         <v>0.98883640519674998</v>
@@ -6866,10 +6800,10 @@
         <v>239</v>
       </c>
       <c r="AE13" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="AF13" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -6884,13 +6818,14 @@
         <v>175</v>
       </c>
       <c r="AL13" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="AM13" t="s">
-        <v>343</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>344</v>
+        <v>326</v>
+      </c>
+      <c r="AN13" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won13</v>
       </c>
       <c r="AO13">
         <v>0.99427708421681416</v>
@@ -6902,10 +6837,10 @@
         <v>239</v>
       </c>
       <c r="AS13" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="AT13" t="s">
-        <v>372</v>
+        <v>349</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -6920,13 +6855,14 @@
         <v>175</v>
       </c>
       <c r="AZ13" t="s">
-        <v>371</v>
+        <v>348</v>
       </c>
       <c r="BA13" t="s">
-        <v>390</v>
-      </c>
-      <c r="BB13" t="s">
-        <v>290</v>
+        <v>366</v>
+      </c>
+      <c r="BB13" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof8</v>
       </c>
       <c r="BC13">
         <v>0.98926313025711288</v>
@@ -6999,8 +6935,9 @@
       <c r="Y14" t="s">
         <v>225</v>
       </c>
-      <c r="Z14" t="s">
-        <v>287</v>
+      <c r="Z14" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol8</v>
       </c>
       <c r="AA14">
         <v>0.99536570131993762</v>
@@ -7012,10 +6949,10 @@
         <v>239</v>
       </c>
       <c r="AE14" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="AF14" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7030,13 +6967,14 @@
         <v>175</v>
       </c>
       <c r="AL14" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="AM14" t="s">
-        <v>345</v>
-      </c>
-      <c r="AN14" t="s">
-        <v>346</v>
+        <v>327</v>
+      </c>
+      <c r="AN14" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won3</v>
       </c>
       <c r="AO14">
         <v>0.99392750374448113</v>
@@ -7048,10 +6986,10 @@
         <v>239</v>
       </c>
       <c r="AS14" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="AT14" t="s">
-        <v>374</v>
+        <v>351</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7066,13 +7004,14 @@
         <v>175</v>
       </c>
       <c r="AZ14" t="s">
-        <v>373</v>
+        <v>350</v>
       </c>
       <c r="BA14" t="s">
-        <v>391</v>
-      </c>
-      <c r="BB14" t="s">
-        <v>388</v>
+        <v>367</v>
+      </c>
+      <c r="BB14" t="str">
+        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA14,2),0,"")&amp;"0"</f>
+        <v>e_wof10</v>
       </c>
       <c r="BC14">
         <v>0.99136264788907857</v>
@@ -7145,8 +7084,9 @@
       <c r="Y15" t="s">
         <v>220</v>
       </c>
-      <c r="Z15" t="s">
-        <v>284</v>
+      <c r="Z15" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol3</v>
       </c>
       <c r="AA15">
         <v>0.99356288436829876</v>
@@ -7158,10 +7098,10 @@
         <v>239</v>
       </c>
       <c r="AE15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="AF15" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7176,13 +7116,14 @@
         <v>175</v>
       </c>
       <c r="AL15" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="AM15" t="s">
-        <v>347</v>
-      </c>
-      <c r="AN15" t="s">
-        <v>293</v>
+        <v>328</v>
+      </c>
+      <c r="AN15" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won14</v>
       </c>
       <c r="AO15">
         <v>0.99368847580230268</v>
@@ -7194,10 +7135,10 @@
         <v>239</v>
       </c>
       <c r="AS15" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="AT15" t="s">
-        <v>376</v>
+        <v>353</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7212,13 +7153,14 @@
         <v>175</v>
       </c>
       <c r="AZ15" t="s">
-        <v>375</v>
+        <v>352</v>
       </c>
       <c r="BA15" t="s">
-        <v>392</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>388</v>
+        <v>368</v>
+      </c>
+      <c r="BB15" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof4</v>
       </c>
       <c r="BC15">
         <v>0.99520217301523817</v>
@@ -7291,8 +7233,9 @@
       <c r="Y16" t="s">
         <v>233</v>
       </c>
-      <c r="Z16" t="s">
-        <v>288</v>
+      <c r="Z16" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol16</v>
       </c>
       <c r="AA16">
         <v>0.99442875744459613</v>
@@ -7304,10 +7247,10 @@
         <v>239</v>
       </c>
       <c r="AE16" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="AF16" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7322,13 +7265,14 @@
         <v>175</v>
       </c>
       <c r="AL16" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="AM16" t="s">
-        <v>348</v>
-      </c>
-      <c r="AN16" t="s">
-        <v>349</v>
+        <v>329</v>
+      </c>
+      <c r="AN16" t="str">
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM16,2),0,"")&amp;"0"</f>
+        <v>e_won20</v>
       </c>
       <c r="AO16">
         <v>0.99582677011152854</v>
@@ -7340,10 +7284,10 @@
         <v>239</v>
       </c>
       <c r="AS16" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="AT16" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7358,13 +7302,14 @@
         <v>175</v>
       </c>
       <c r="AZ16" t="s">
-        <v>377</v>
+        <v>354</v>
       </c>
       <c r="BA16" t="s">
-        <v>393</v>
-      </c>
-      <c r="BB16" t="s">
-        <v>388</v>
+        <v>369</v>
+      </c>
+      <c r="BB16" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof5</v>
       </c>
       <c r="BC16">
         <v>0.99136108064447537</v>
@@ -7437,8 +7382,9 @@
       <c r="Y17" t="s">
         <v>229</v>
       </c>
-      <c r="Z17" t="s">
-        <v>289</v>
+      <c r="Z17" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol12</v>
       </c>
       <c r="AA17">
         <v>0.99131060083308187</v>
@@ -7450,10 +7396,10 @@
         <v>239</v>
       </c>
       <c r="AE17" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="AF17" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7468,13 +7414,14 @@
         <v>175</v>
       </c>
       <c r="AL17" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="AM17" t="s">
-        <v>350</v>
-      </c>
-      <c r="AN17" t="s">
-        <v>291</v>
+        <v>330</v>
+      </c>
+      <c r="AN17" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won15</v>
       </c>
       <c r="AO17">
         <v>0.9911442551729287</v>
@@ -7486,10 +7433,10 @@
         <v>239</v>
       </c>
       <c r="AS17" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="AT17" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7504,13 +7451,14 @@
         <v>175</v>
       </c>
       <c r="AZ17" t="s">
-        <v>379</v>
+        <v>356</v>
       </c>
       <c r="BA17" t="s">
-        <v>394</v>
-      </c>
-      <c r="BB17" t="s">
-        <v>287</v>
+        <v>370</v>
+      </c>
+      <c r="BB17" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof2</v>
       </c>
       <c r="BC17">
         <v>0.98954715343009803</v>
@@ -7583,8 +7531,9 @@
       <c r="Y18" t="s">
         <v>221</v>
       </c>
-      <c r="Z18" t="s">
-        <v>290</v>
+      <c r="Z18" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol4</v>
       </c>
       <c r="AA18">
         <v>0.99559401474611386</v>
@@ -7596,10 +7545,10 @@
         <v>239</v>
       </c>
       <c r="AE18" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="AF18" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7614,13 +7563,14 @@
         <v>175</v>
       </c>
       <c r="AL18" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="AM18" t="s">
-        <v>351</v>
-      </c>
-      <c r="AN18" t="s">
-        <v>294</v>
+        <v>331</v>
+      </c>
+      <c r="AN18" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won7</v>
       </c>
       <c r="AO18">
         <v>0.99353102787032765</v>
@@ -7632,10 +7582,10 @@
         <v>239</v>
       </c>
       <c r="AS18" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="AT18" t="s">
-        <v>382</v>
+        <v>359</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7650,13 +7600,14 @@
         <v>175</v>
       </c>
       <c r="AZ18" t="s">
-        <v>381</v>
+        <v>358</v>
       </c>
       <c r="BA18" t="s">
-        <v>395</v>
-      </c>
-      <c r="BB18" t="s">
-        <v>388</v>
+        <v>371</v>
+      </c>
+      <c r="BB18" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof9</v>
       </c>
       <c r="BC18">
         <v>0.99333526531977001</v>
@@ -7729,8 +7680,9 @@
       <c r="Y19" t="s">
         <v>232</v>
       </c>
-      <c r="Z19" t="s">
-        <v>291</v>
+      <c r="Z19" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol15</v>
       </c>
       <c r="AA19">
         <v>0.99589633147839685</v>
@@ -7742,10 +7694,10 @@
         <v>239</v>
       </c>
       <c r="AE19" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="AF19" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -7760,13 +7712,14 @@
         <v>175</v>
       </c>
       <c r="AL19" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="AM19" t="s">
-        <v>352</v>
-      </c>
-      <c r="AN19" t="s">
-        <v>297</v>
+        <v>332</v>
+      </c>
+      <c r="AN19" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won5</v>
       </c>
       <c r="AO19">
         <v>0.98751891498768063</v>
@@ -7778,10 +7731,10 @@
         <v>239</v>
       </c>
       <c r="AS19" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="AT19" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7796,13 +7749,14 @@
         <v>175</v>
       </c>
       <c r="AZ19" t="s">
-        <v>383</v>
+        <v>360</v>
       </c>
       <c r="BA19" t="s">
-        <v>396</v>
-      </c>
-      <c r="BB19" t="s">
-        <v>287</v>
+        <v>372</v>
+      </c>
+      <c r="BB19" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof1</v>
       </c>
       <c r="BC19">
         <v>0.9941446088905187</v>
@@ -7875,8 +7829,9 @@
       <c r="Y20" t="s">
         <v>237</v>
       </c>
-      <c r="Z20" t="s">
-        <v>286</v>
+      <c r="Z20" t="str">
+        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y20,2),0,"")&amp;"0"</f>
+        <v>e_sol20</v>
       </c>
       <c r="AA20">
         <v>0.9962937079492431</v>
@@ -7888,10 +7843,10 @@
         <v>239</v>
       </c>
       <c r="AE20" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="AF20" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -7906,13 +7861,14 @@
         <v>175</v>
       </c>
       <c r="AL20" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="AM20" t="s">
-        <v>353</v>
-      </c>
-      <c r="AN20" t="s">
-        <v>344</v>
+        <v>333</v>
+      </c>
+      <c r="AN20" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won11</v>
       </c>
       <c r="AO20">
         <v>0.98768981100926756</v>
@@ -7924,10 +7880,10 @@
         <v>239</v>
       </c>
       <c r="AS20" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="AT20" t="s">
-        <v>386</v>
+        <v>363</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -7942,13 +7898,14 @@
         <v>175</v>
       </c>
       <c r="AZ20" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="BA20" t="s">
-        <v>397</v>
-      </c>
-      <c r="BB20" t="s">
-        <v>287</v>
+        <v>373</v>
+      </c>
+      <c r="BB20" t="str">
+        <f t="shared" si="2"/>
+        <v>e_wof3</v>
       </c>
       <c r="BC20">
         <v>0.99204351007823377</v>
@@ -8021,8 +7978,9 @@
       <c r="Y21" t="s">
         <v>224</v>
       </c>
-      <c r="Z21" t="s">
-        <v>292</v>
+      <c r="Z21" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol7</v>
       </c>
       <c r="AA21">
         <v>0.99371757160137486</v>
@@ -8034,10 +7992,10 @@
         <v>239</v>
       </c>
       <c r="AE21" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AF21" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8052,13 +8010,14 @@
         <v>175</v>
       </c>
       <c r="AL21" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="AM21" t="s">
-        <v>354</v>
-      </c>
-      <c r="AN21" t="s">
-        <v>355</v>
+        <v>334</v>
+      </c>
+      <c r="AN21" t="str">
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM21,2),0,"")&amp;"0"</f>
+        <v>e_won10</v>
       </c>
       <c r="AO21">
         <v>0.99419279872301636</v>
@@ -8131,8 +8090,9 @@
       <c r="Y22" t="s">
         <v>222</v>
       </c>
-      <c r="Z22" t="s">
-        <v>293</v>
+      <c r="Z22" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol5</v>
       </c>
       <c r="AA22">
         <v>0.99372835533859694</v>
@@ -8144,10 +8104,10 @@
         <v>239</v>
       </c>
       <c r="AE22" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="AF22" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8162,13 +8122,14 @@
         <v>175</v>
       </c>
       <c r="AL22" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="AM22" t="s">
-        <v>356</v>
-      </c>
-      <c r="AN22" t="s">
-        <v>289</v>
+        <v>335</v>
+      </c>
+      <c r="AN22" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won16</v>
       </c>
       <c r="AO22">
         <v>0.99053113122064196</v>
@@ -8241,8 +8202,9 @@
       <c r="Y23" t="s">
         <v>234</v>
       </c>
-      <c r="Z23" t="s">
-        <v>288</v>
+      <c r="Z23" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol17</v>
       </c>
       <c r="AA23">
         <v>0.9964587744572686</v>
@@ -8254,10 +8216,10 @@
         <v>239</v>
       </c>
       <c r="AE23" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="AF23" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8272,13 +8234,14 @@
         <v>175</v>
       </c>
       <c r="AL23" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="AM23" t="s">
-        <v>357</v>
-      </c>
-      <c r="AN23" t="s">
-        <v>358</v>
+        <v>336</v>
+      </c>
+      <c r="AN23" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won12</v>
       </c>
       <c r="AO23">
         <v>0.99436493305946672</v>
@@ -8351,8 +8314,9 @@
       <c r="Y24" t="s">
         <v>235</v>
       </c>
-      <c r="Z24" t="s">
-        <v>294</v>
+      <c r="Z24" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol18</v>
       </c>
       <c r="AA24">
         <v>0.99630851076955973</v>
@@ -8364,10 +8328,10 @@
         <v>239</v>
       </c>
       <c r="AE24" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="AF24" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8382,13 +8346,14 @@
         <v>175</v>
       </c>
       <c r="AL24" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="AM24" t="s">
-        <v>359</v>
-      </c>
-      <c r="AN24" t="s">
-        <v>288</v>
+        <v>337</v>
+      </c>
+      <c r="AN24" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won6</v>
       </c>
       <c r="AO24">
         <v>0.99558761976621801</v>
@@ -8461,8 +8426,9 @@
       <c r="Y25" t="s">
         <v>231</v>
       </c>
-      <c r="Z25" t="s">
-        <v>295</v>
+      <c r="Z25" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol14</v>
       </c>
       <c r="AA25">
         <v>0.99306360188977116</v>
@@ -8474,10 +8440,10 @@
         <v>239</v>
       </c>
       <c r="AE25" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="AF25" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8492,13 +8458,14 @@
         <v>175</v>
       </c>
       <c r="AL25" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="AM25" t="s">
-        <v>360</v>
-      </c>
-      <c r="AN25" t="s">
-        <v>361</v>
+        <v>338</v>
+      </c>
+      <c r="AN25" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won19</v>
       </c>
       <c r="AO25">
         <v>0.99520787559028878</v>
@@ -8571,8 +8538,9 @@
       <c r="Y26" t="s">
         <v>223</v>
       </c>
-      <c r="Z26" t="s">
-        <v>296</v>
+      <c r="Z26" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol6</v>
       </c>
       <c r="AA26">
         <v>0.990012010348303</v>
@@ -8584,10 +8552,10 @@
         <v>239</v>
       </c>
       <c r="AE26" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="AF26" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -8602,13 +8570,14 @@
         <v>175</v>
       </c>
       <c r="AL26" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="AM26" t="s">
-        <v>362</v>
-      </c>
-      <c r="AN26" t="s">
-        <v>287</v>
+        <v>339</v>
+      </c>
+      <c r="AN26" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won9</v>
       </c>
       <c r="AO26">
         <v>0.99552303355529737</v>
@@ -8681,8 +8650,9 @@
       <c r="Y27" t="s">
         <v>228</v>
       </c>
-      <c r="Z27" t="s">
-        <v>294</v>
+      <c r="Z27" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol11</v>
       </c>
       <c r="AA27">
         <v>0.98893381891519438</v>
@@ -8694,10 +8664,10 @@
         <v>239</v>
       </c>
       <c r="AE27" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AF27" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -8712,13 +8682,14 @@
         <v>175</v>
       </c>
       <c r="AL27" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="AM27" t="s">
-        <v>363</v>
-      </c>
-      <c r="AN27" t="s">
-        <v>289</v>
+        <v>340</v>
+      </c>
+      <c r="AN27" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won17</v>
       </c>
       <c r="AO27">
         <v>0.9913766042890243</v>
@@ -8791,8 +8762,9 @@
       <c r="Y28" t="s">
         <v>227</v>
       </c>
-      <c r="Z28" t="s">
-        <v>294</v>
+      <c r="Z28" t="str">
+        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y28,2),0,"")&amp;"0"</f>
+        <v>e_sol10</v>
       </c>
       <c r="AA28">
         <v>0.9866385672597856</v>
@@ -8804,10 +8776,10 @@
         <v>239</v>
       </c>
       <c r="AE28" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AF28" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -8822,13 +8794,14 @@
         <v>175</v>
       </c>
       <c r="AL28" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="AM28" t="s">
-        <v>364</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>286</v>
+        <v>341</v>
+      </c>
+      <c r="AN28" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won2</v>
       </c>
       <c r="AO28">
         <v>0.99498199124719422</v>
@@ -8901,8 +8874,9 @@
       <c r="Y29" t="s">
         <v>226</v>
       </c>
-      <c r="Z29" t="s">
-        <v>297</v>
+      <c r="Z29" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol9</v>
       </c>
       <c r="AA29">
         <v>0.98928494645383225</v>
@@ -8914,10 +8888,10 @@
         <v>239</v>
       </c>
       <c r="AE29" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AF29" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -8932,13 +8906,14 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="AM29" t="s">
-        <v>365</v>
-      </c>
-      <c r="AN29" t="s">
-        <v>284</v>
+        <v>342</v>
+      </c>
+      <c r="AN29" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won18</v>
       </c>
       <c r="AO29">
         <v>0.98926286248458195</v>
@@ -9011,8 +8986,9 @@
       <c r="Y30" t="s">
         <v>218</v>
       </c>
-      <c r="Z30" t="s">
-        <v>298</v>
+      <c r="Z30" t="str">
+        <f t="shared" si="0"/>
+        <v>e_sol1</v>
       </c>
       <c r="AA30">
         <v>0.9905299918588647</v>
@@ -9024,10 +9000,10 @@
         <v>239</v>
       </c>
       <c r="AE30" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AF30" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -9042,13 +9018,14 @@
         <v>175</v>
       </c>
       <c r="AL30" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="AM30" t="s">
-        <v>366</v>
-      </c>
-      <c r="AN30" t="s">
-        <v>289</v>
+        <v>343</v>
+      </c>
+      <c r="AN30" t="str">
+        <f t="shared" si="1"/>
+        <v>e_won4</v>
       </c>
       <c r="AO30">
         <v>0.98909696821272286</v>
@@ -9154,10 +9131,10 @@
         <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="D11" t="s">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9172,10 +9149,10 @@
         <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="K11" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="L11">
         <v>0.45167200935612223</v>
@@ -9187,10 +9164,10 @@
         <v>171</v>
       </c>
       <c r="P11" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="Q11" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9205,10 +9182,10 @@
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="X11" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -9222,10 +9199,10 @@
         <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9240,10 +9217,10 @@
         <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="K12" t="s">
-        <v>364</v>
+        <v>341</v>
       </c>
       <c r="L12">
         <v>0.50504353376491207</v>
@@ -9255,10 +9232,10 @@
         <v>171</v>
       </c>
       <c r="P12" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="Q12" t="s">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9273,10 +9250,10 @@
         <v>175</v>
       </c>
       <c r="W12" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="X12" t="s">
-        <v>394</v>
+        <v>370</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -9290,10 +9267,10 @@
         <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="D13" t="s">
-        <v>403</v>
+        <v>379</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9308,10 +9285,10 @@
         <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="K13" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="L13">
         <v>1.7897871713950226</v>
@@ -9323,10 +9300,10 @@
         <v>171</v>
       </c>
       <c r="P13" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="Q13" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -9341,10 +9318,10 @@
         <v>175</v>
       </c>
       <c r="W13" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="X13" t="s">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -9358,10 +9335,10 @@
         <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="D14" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -9376,10 +9353,10 @@
         <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="K14" t="s">
-        <v>366</v>
+        <v>343</v>
       </c>
       <c r="L14">
         <v>2.6804732670444085</v>
@@ -9391,10 +9368,10 @@
         <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="Q14" t="s">
-        <v>445</v>
+        <v>421</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -9409,10 +9386,10 @@
         <v>175</v>
       </c>
       <c r="W14" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="X14" t="s">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9426,10 +9403,10 @@
         <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="D15" t="s">
-        <v>407</v>
+        <v>383</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -9444,10 +9421,10 @@
         <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="K15" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="L15">
         <v>8.0517810049421517</v>
@@ -9459,10 +9436,10 @@
         <v>171</v>
       </c>
       <c r="P15" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="Q15" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -9477,10 +9454,10 @@
         <v>175</v>
       </c>
       <c r="W15" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="X15" t="s">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9494,10 +9471,10 @@
         <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>409</v>
+        <v>385</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -9512,10 +9489,10 @@
         <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>408</v>
+        <v>384</v>
       </c>
       <c r="K16" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="L16">
         <v>0.96273897344398884</v>
@@ -9527,10 +9504,10 @@
         <v>171</v>
       </c>
       <c r="P16" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="Q16" t="s">
-        <v>449</v>
+        <v>425</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -9545,10 +9522,10 @@
         <v>175</v>
       </c>
       <c r="W16" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="X16" t="s">
-        <v>387</v>
+        <v>364</v>
       </c>
       <c r="Y16">
         <v>10.023</v>
@@ -9562,10 +9539,10 @@
         <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="D17" t="s">
-        <v>411</v>
+        <v>387</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -9580,10 +9557,10 @@
         <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>410</v>
+        <v>386</v>
       </c>
       <c r="K17" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="L17">
         <v>1.093890418371007</v>
@@ -9595,10 +9572,10 @@
         <v>171</v>
       </c>
       <c r="P17" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="Q17" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -9613,10 +9590,10 @@
         <v>175</v>
       </c>
       <c r="W17" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="X17" t="s">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -9630,10 +9607,10 @@
         <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>389</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -9648,10 +9625,10 @@
         <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>412</v>
+        <v>388</v>
       </c>
       <c r="K18" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="L18">
         <v>3.1665724666245323</v>
@@ -9663,10 +9640,10 @@
         <v>171</v>
       </c>
       <c r="P18" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="Q18" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -9681,10 +9658,10 @@
         <v>175</v>
       </c>
       <c r="W18" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="X18" t="s">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9698,10 +9675,10 @@
         <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="D19" t="s">
-        <v>415</v>
+        <v>391</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -9716,10 +9693,10 @@
         <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>414</v>
+        <v>390</v>
       </c>
       <c r="K19" t="s">
-        <v>362</v>
+        <v>339</v>
       </c>
       <c r="L19">
         <v>0.55491188155257321</v>
@@ -9731,10 +9708,10 @@
         <v>171</v>
       </c>
       <c r="P19" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="Q19" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -9749,10 +9726,10 @@
         <v>175</v>
       </c>
       <c r="W19" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="X19" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9766,10 +9743,10 @@
         <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="D20" t="s">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -9784,10 +9761,10 @@
         <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="K20" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="L20">
         <v>0.97886072674627833</v>
@@ -9799,10 +9776,10 @@
         <v>171</v>
       </c>
       <c r="P20" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="Q20" t="s">
-        <v>457</v>
+        <v>433</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -9817,10 +9794,10 @@
         <v>175</v>
       </c>
       <c r="W20" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="X20" t="s">
-        <v>391</v>
+        <v>367</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9834,10 +9811,10 @@
         <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="D21" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -9852,10 +9829,10 @@
         <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="K21" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="L21">
         <v>0.40593208719379742</v>
@@ -9869,10 +9846,10 @@
         <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="D22" t="s">
-        <v>421</v>
+        <v>397</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -9887,10 +9864,10 @@
         <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="K22" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="L22">
         <v>0.8833561507867439</v>
@@ -9904,10 +9881,10 @@
         <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="D23" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -9922,10 +9899,10 @@
         <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="K23" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="L23">
         <v>0.40306698622644632</v>
@@ -9939,10 +9916,10 @@
         <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="D24" t="s">
-        <v>425</v>
+        <v>401</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -9957,10 +9934,10 @@
         <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="K24" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="L24">
         <v>0.84020182400735144</v>
@@ -9974,10 +9951,10 @@
         <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="D25" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -9992,10 +9969,10 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="K25" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -10009,10 +9986,10 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D26" t="s">
-        <v>429</v>
+        <v>405</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -10027,10 +10004,10 @@
         <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="K26" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="L26">
         <v>0.89446396558783758</v>
@@ -10044,10 +10021,10 @@
         <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="D27" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -10062,10 +10039,10 @@
         <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="K27" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10079,10 +10056,10 @@
         <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="D28" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -10097,10 +10074,10 @@
         <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="K28" t="s">
-        <v>365</v>
+        <v>342</v>
       </c>
       <c r="L28">
         <v>1.4637274230737423</v>
@@ -10114,10 +10091,10 @@
         <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="D29" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -10132,10 +10109,10 @@
         <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="K29" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="L29">
         <v>0.63042801517356961</v>
@@ -10149,10 +10126,10 @@
         <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="D30" t="s">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -10167,10 +10144,10 @@
         <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="K30" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="L30">
         <v>0.61343702722931326</v>
@@ -10243,7 +10220,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -10267,7 +10244,7 @@
         <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -10279,12 +10256,12 @@
         <v>243</v>
       </c>
       <c r="P11" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -10302,13 +10279,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="J12" t="s">
         <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -10320,12 +10297,12 @@
         <v>243</v>
       </c>
       <c r="P12" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -10343,13 +10320,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J13" t="s">
         <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -10361,12 +10338,12 @@
         <v>243</v>
       </c>
       <c r="P13" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -10384,13 +10361,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="J14" t="s">
         <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -10402,12 +10379,12 @@
         <v>243</v>
       </c>
       <c r="P14" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -10425,13 +10402,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="J15" t="s">
         <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -10443,12 +10420,12 @@
         <v>243</v>
       </c>
       <c r="P15" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -10472,7 +10449,7 @@
         <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -10484,12 +10461,12 @@
         <v>243</v>
       </c>
       <c r="P16" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -10507,13 +10484,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="J17" t="s">
         <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -10525,12 +10502,12 @@
         <v>243</v>
       </c>
       <c r="P17" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -10548,13 +10525,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J18" t="s">
         <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -10566,12 +10543,12 @@
         <v>243</v>
       </c>
       <c r="P18" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -10589,13 +10566,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -10607,12 +10584,12 @@
         <v>243</v>
       </c>
       <c r="P19" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -10630,13 +10607,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="J20" t="s">
         <v>171</v>
       </c>
       <c r="K20" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -10648,12 +10625,12 @@
         <v>243</v>
       </c>
       <c r="P20" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -10677,7 +10654,7 @@
         <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -10689,12 +10666,12 @@
         <v>243</v>
       </c>
       <c r="P21" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -10712,13 +10689,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J22" t="s">
         <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -10730,12 +10707,12 @@
         <v>243</v>
       </c>
       <c r="P22" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>464</v>
+        <v>440</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -10753,13 +10730,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="J23" t="s">
         <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -10771,12 +10748,12 @@
         <v>243</v>
       </c>
       <c r="P23" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -10800,7 +10777,7 @@
         <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -10812,12 +10789,12 @@
         <v>243</v>
       </c>
       <c r="P24" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -10835,13 +10812,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="J25" t="s">
         <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -10853,12 +10830,12 @@
         <v>243</v>
       </c>
       <c r="P25" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -10876,13 +10853,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="J26" t="s">
         <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -10894,12 +10871,12 @@
         <v>243</v>
       </c>
       <c r="P26" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -10923,7 +10900,7 @@
         <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -10935,12 +10912,12 @@
         <v>243</v>
       </c>
       <c r="P27" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -10958,12 +10935,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -10981,12 +10958,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11009,7 +10986,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11027,12 +11004,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11050,12 +11027,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -11078,7 +11055,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -11096,12 +11073,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -11119,12 +11096,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -11142,12 +11119,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -11165,12 +11142,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -11193,7 +11170,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -11211,12 +11188,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -11234,12 +11211,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -11262,7 +11239,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11280,12 +11257,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11303,12 +11280,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -11331,7 +11308,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -11349,12 +11326,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -11372,12 +11349,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11400,7 +11377,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11418,12 +11395,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11441,12 +11418,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -11469,7 +11446,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -11487,12 +11464,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -11510,12 +11487,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -11533,12 +11510,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -11556,12 +11533,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -11584,7 +11561,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -11602,12 +11579,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -11625,12 +11602,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -11653,7 +11630,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -11671,12 +11648,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -11694,12 +11671,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -11722,7 +11699,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -11740,12 +11717,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -11763,15 +11740,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C64" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -11791,10 +11768,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C65" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -11809,15 +11786,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C66" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -11832,15 +11809,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C67" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -11855,15 +11832,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="C68" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -11878,15 +11855,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C69" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -11906,10 +11883,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C70" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -11924,15 +11901,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C71" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -11947,15 +11924,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C72" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -11970,15 +11947,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="C73" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -11993,7 +11970,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{017B7459-A9A6-40CB-A8A5-5EE8621F4FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B10FEEE-0177-413C-B829-40F113968019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6526,8 +6526,8 @@
         <v>324</v>
       </c>
       <c r="AN11" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM11,2),0,"")</f>
-        <v>e_won1</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM11,2),0,"")+20</f>
+        <v>e_won21</v>
       </c>
       <c r="AO11">
         <v>0.99363378101904942</v>
@@ -6563,8 +6563,8 @@
         <v>364</v>
       </c>
       <c r="BB11" t="str">
-        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA11,2),0,"")</f>
-        <v>e_wof6</v>
+        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA11,2),0,"")+40</f>
+        <v>e_wof46</v>
       </c>
       <c r="BC11">
         <v>0.99653064315884643</v>
@@ -6675,8 +6675,8 @@
         <v>325</v>
       </c>
       <c r="AN12" t="str">
-        <f t="shared" ref="AN12:AN30" si="1">"e_won"&amp;SUBSTITUTE(RIGHT(AM12,2),0,"")</f>
-        <v>e_won8</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM12,2),0,"")+20</f>
+        <v>e_won28</v>
       </c>
       <c r="AO12">
         <v>0.98844945266915318</v>
@@ -6712,8 +6712,8 @@
         <v>365</v>
       </c>
       <c r="BB12" t="str">
-        <f t="shared" ref="BB12:BB20" si="2">"e_wof"&amp;SUBSTITUTE(RIGHT(BA12,2),0,"")</f>
-        <v>e_wof7</v>
+        <f t="shared" ref="BB12:BB20" si="1">"e_wof"&amp;SUBSTITUTE(RIGHT(BA12,2),0,"")+40</f>
+        <v>e_wof47</v>
       </c>
       <c r="BC12">
         <v>0.99207591869454059</v>
@@ -6824,8 +6824,8 @@
         <v>326</v>
       </c>
       <c r="AN13" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won13</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM13,2),0,"")+20</f>
+        <v>e_won33</v>
       </c>
       <c r="AO13">
         <v>0.99427708421681416</v>
@@ -6861,8 +6861,8 @@
         <v>366</v>
       </c>
       <c r="BB13" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof8</v>
+        <f t="shared" si="1"/>
+        <v>e_wof48</v>
       </c>
       <c r="BC13">
         <v>0.98926313025711288</v>
@@ -6973,8 +6973,8 @@
         <v>327</v>
       </c>
       <c r="AN14" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won3</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM14,2),0,"")+20</f>
+        <v>e_won23</v>
       </c>
       <c r="AO14">
         <v>0.99392750374448113</v>
@@ -7010,8 +7010,8 @@
         <v>367</v>
       </c>
       <c r="BB14" t="str">
-        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA14,2),0,"")&amp;"0"</f>
-        <v>e_wof10</v>
+        <f t="shared" si="1"/>
+        <v>e_wof41</v>
       </c>
       <c r="BC14">
         <v>0.99136264788907857</v>
@@ -7122,8 +7122,8 @@
         <v>328</v>
       </c>
       <c r="AN15" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won14</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM15,2),0,"")+20</f>
+        <v>e_won34</v>
       </c>
       <c r="AO15">
         <v>0.99368847580230268</v>
@@ -7159,8 +7159,8 @@
         <v>368</v>
       </c>
       <c r="BB15" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof4</v>
+        <f t="shared" si="1"/>
+        <v>e_wof44</v>
       </c>
       <c r="BC15">
         <v>0.99520217301523817</v>
@@ -7271,8 +7271,8 @@
         <v>329</v>
       </c>
       <c r="AN16" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM16,2),0,"")&amp;"0"</f>
-        <v>e_won20</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM16,2),0,"")+20</f>
+        <v>e_won22</v>
       </c>
       <c r="AO16">
         <v>0.99582677011152854</v>
@@ -7308,8 +7308,8 @@
         <v>369</v>
       </c>
       <c r="BB16" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof5</v>
+        <f t="shared" si="1"/>
+        <v>e_wof45</v>
       </c>
       <c r="BC16">
         <v>0.99136108064447537</v>
@@ -7420,8 +7420,8 @@
         <v>330</v>
       </c>
       <c r="AN17" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won15</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM17,2),0,"")+20</f>
+        <v>e_won35</v>
       </c>
       <c r="AO17">
         <v>0.9911442551729287</v>
@@ -7457,8 +7457,8 @@
         <v>370</v>
       </c>
       <c r="BB17" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof2</v>
+        <f t="shared" si="1"/>
+        <v>e_wof42</v>
       </c>
       <c r="BC17">
         <v>0.98954715343009803</v>
@@ -7569,8 +7569,8 @@
         <v>331</v>
       </c>
       <c r="AN18" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won7</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM18,2),0,"")+20</f>
+        <v>e_won27</v>
       </c>
       <c r="AO18">
         <v>0.99353102787032765</v>
@@ -7606,8 +7606,8 @@
         <v>371</v>
       </c>
       <c r="BB18" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof9</v>
+        <f t="shared" si="1"/>
+        <v>e_wof49</v>
       </c>
       <c r="BC18">
         <v>0.99333526531977001</v>
@@ -7718,8 +7718,8 @@
         <v>332</v>
       </c>
       <c r="AN19" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won5</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM19,2),0,"")+20</f>
+        <v>e_won25</v>
       </c>
       <c r="AO19">
         <v>0.98751891498768063</v>
@@ -7755,8 +7755,8 @@
         <v>372</v>
       </c>
       <c r="BB19" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof1</v>
+        <f t="shared" si="1"/>
+        <v>e_wof41</v>
       </c>
       <c r="BC19">
         <v>0.9941446088905187</v>
@@ -7867,8 +7867,8 @@
         <v>333</v>
       </c>
       <c r="AN20" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won11</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM20,2),0,"")+20</f>
+        <v>e_won31</v>
       </c>
       <c r="AO20">
         <v>0.98768981100926756</v>
@@ -7904,8 +7904,8 @@
         <v>373</v>
       </c>
       <c r="BB20" t="str">
-        <f t="shared" si="2"/>
-        <v>e_wof3</v>
+        <f t="shared" si="1"/>
+        <v>e_wof43</v>
       </c>
       <c r="BC20">
         <v>0.99204351007823377</v>
@@ -8016,8 +8016,8 @@
         <v>334</v>
       </c>
       <c r="AN21" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM21,2),0,"")&amp;"0"</f>
-        <v>e_won10</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM21,2),0,"")+20</f>
+        <v>e_won21</v>
       </c>
       <c r="AO21">
         <v>0.99419279872301636</v>
@@ -8128,8 +8128,8 @@
         <v>335</v>
       </c>
       <c r="AN22" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won16</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM22,2),0,"")+20</f>
+        <v>e_won36</v>
       </c>
       <c r="AO22">
         <v>0.99053113122064196</v>
@@ -8240,8 +8240,8 @@
         <v>336</v>
       </c>
       <c r="AN23" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won12</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM23,2),0,"")+20</f>
+        <v>e_won32</v>
       </c>
       <c r="AO23">
         <v>0.99436493305946672</v>
@@ -8352,8 +8352,8 @@
         <v>337</v>
       </c>
       <c r="AN24" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won6</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM24,2),0,"")+20</f>
+        <v>e_won26</v>
       </c>
       <c r="AO24">
         <v>0.99558761976621801</v>
@@ -8464,8 +8464,8 @@
         <v>338</v>
       </c>
       <c r="AN25" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won19</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM25,2),0,"")+20</f>
+        <v>e_won39</v>
       </c>
       <c r="AO25">
         <v>0.99520787559028878</v>
@@ -8576,8 +8576,8 @@
         <v>339</v>
       </c>
       <c r="AN26" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won9</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM26,2),0,"")+20</f>
+        <v>e_won29</v>
       </c>
       <c r="AO26">
         <v>0.99552303355529737</v>
@@ -8688,8 +8688,8 @@
         <v>340</v>
       </c>
       <c r="AN27" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won17</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM27,2),0,"")+20</f>
+        <v>e_won37</v>
       </c>
       <c r="AO27">
         <v>0.9913766042890243</v>
@@ -8800,8 +8800,8 @@
         <v>341</v>
       </c>
       <c r="AN28" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won2</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM28,2),0,"")+20</f>
+        <v>e_won22</v>
       </c>
       <c r="AO28">
         <v>0.99498199124719422</v>
@@ -8912,8 +8912,8 @@
         <v>342</v>
       </c>
       <c r="AN29" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won18</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM29,2),0,"")+20</f>
+        <v>e_won38</v>
       </c>
       <c r="AO29">
         <v>0.98926286248458195</v>
@@ -9024,8 +9024,8 @@
         <v>343</v>
       </c>
       <c r="AN30" t="str">
-        <f t="shared" si="1"/>
-        <v>e_won4</v>
+        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM30,2),0,"")+20</f>
+        <v>e_won24</v>
       </c>
       <c r="AO30">
         <v>0.98909696821272286</v>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B10FEEE-0177-413C-B829-40F113968019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{582EE015-2889-4C4F-9D6D-1B7EDFA6F16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="507">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -849,16 +849,118 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_002</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 2</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_solelc_spv_019</t>
@@ -867,298 +969,346 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_020</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_sol1</t>
+  </si>
+  <si>
+    <t>e_sol2</t>
+  </si>
+  <si>
+    <t>e_sol3</t>
+  </si>
+  <si>
+    <t>e_sol4</t>
+  </si>
+  <si>
+    <t>e_sol5</t>
+  </si>
+  <si>
+    <t>e_sol6</t>
+  </si>
+  <si>
+    <t>e_sol7</t>
+  </si>
+  <si>
+    <t>e_sol8</t>
+  </si>
+  <si>
+    <t>e_sol9</t>
+  </si>
+  <si>
+    <t>e_sol10</t>
+  </si>
+  <si>
+    <t>e_sol11</t>
+  </si>
+  <si>
+    <t>e_sol12</t>
+  </si>
+  <si>
+    <t>e_sol13</t>
+  </si>
+  <si>
+    <t>e_sol14</t>
+  </si>
+  <si>
+    <t>e_sol15</t>
+  </si>
+  <si>
+    <t>e_sol16</t>
+  </si>
+  <si>
+    <t>e_sol17</t>
+  </si>
+  <si>
+    <t>e_sol18</t>
+  </si>
+  <si>
+    <t>e_sol19</t>
+  </si>
+  <si>
+    <t>e_sol20</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_001</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_014</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_020</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_won_001</t>
   </si>
   <si>
+    <t>e_won1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_won2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_won3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_won4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_won5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_won6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_won7</t>
+  </si>
+  <si>
     <t>elc_won_008</t>
   </si>
   <si>
+    <t>e_won8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_won9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_won10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_won11</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_won12</t>
+  </si>
+  <si>
     <t>elc_won_013</t>
   </si>
   <si>
-    <t>elc_won_003</t>
+    <t>e_won13</t>
   </si>
   <si>
     <t>elc_won_014</t>
   </si>
   <si>
+    <t>e_won14</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_won15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_won16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_won17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_won18</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_won19</t>
+  </si>
+  <si>
     <t>elc_won_020</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
+    <t>e_won20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wofelc_wof_006</t>
@@ -1179,76 +1329,76 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_010</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_wof1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_wof2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_wof3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_wof4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_wof5</t>
   </si>
   <si>
     <t>elc_wof_006</t>
   </si>
   <si>
+    <t>e_wof6</t>
+  </si>
+  <si>
     <t>elc_wof_007</t>
   </si>
   <si>
+    <t>e_wof7</t>
+  </si>
+  <si>
     <t>elc_wof_008</t>
   </si>
   <si>
+    <t>e_wof8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_wof9</t>
+  </si>
+  <si>
     <t>elc_wof_010</t>
   </si>
   <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
+    <t>e_wof10</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -1498,12 +1648,6 @@
   </si>
   <si>
     <t>yes</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen1</t>
-  </si>
-  <si>
-    <t>AF</t>
   </si>
 </sst>
 </file>
@@ -2007,7 +2151,7 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2400,7 +2544,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2898,9 +3041,6 @@
       <c r="S12" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="T12" s="148" t="s">
-        <v>458</v>
-      </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
@@ -3401,7 +3541,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_gen3,e_gen1</v>
+        <v>ELC</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3414,9 +3554,6 @@
       </c>
       <c r="S27">
         <v>50</v>
-      </c>
-      <c r="T27">
-        <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="2:22">
@@ -3426,7 +3563,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_gen3,e_gen1</v>
+        <v>ELC</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3441,7 +3578,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>457</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4987,25 +5124,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="149" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="150" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="149"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="149" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="149"/>
-      <c r="K1" s="149"/>
-      <c r="L1" s="149"/>
-      <c r="M1" s="149"/>
-      <c r="N1" s="149"/>
-      <c r="O1" s="152" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5051,7 +5188,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="153"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5096,7 +5233,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="153"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5138,7 +5275,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="154"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6243,14 +6380,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AF485E7-94C5-4D13-98B7-6F397677E2A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F9912-AEDE-4DAE-BE1C-3A1E3CF1C745}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="25" max="25" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="11.19921875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="10.796875" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="9" spans="2:56">
       <c r="B9" t="s">
@@ -6486,26 +6618,25 @@
         <v>240</v>
       </c>
       <c r="Y11" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z11" t="str">
-        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y11,2),0,"")</f>
-        <v>e_sol2</v>
+        <v>218</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>284</v>
       </c>
       <c r="AA11">
-        <v>0.98911580324852866</v>
+        <v>0.9905299918588647</v>
       </c>
       <c r="AB11">
-        <v>199.54360711030768</v>
+        <v>173.61681592081291</v>
       </c>
       <c r="AD11" t="s">
         <v>239</v>
       </c>
       <c r="AE11" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="AF11" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6520,14 +6651,13 @@
         <v>175</v>
       </c>
       <c r="AL11" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="AM11" t="s">
-        <v>324</v>
-      </c>
-      <c r="AN11" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM11,2),0,"")+20</f>
-        <v>e_won21</v>
+        <v>344</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>345</v>
       </c>
       <c r="AO11">
         <v>0.99363378101904942</v>
@@ -6539,10 +6669,10 @@
         <v>239</v>
       </c>
       <c r="AS11" t="s">
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="AT11" t="s">
-        <v>345</v>
+        <v>385</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6557,20 +6687,19 @@
         <v>175</v>
       </c>
       <c r="AZ11" t="s">
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="BA11" t="s">
-        <v>364</v>
-      </c>
-      <c r="BB11" t="str">
-        <f>"e_wof"&amp;SUBSTITUTE(RIGHT(BA11,2),0,"")+40</f>
-        <v>e_wof46</v>
+        <v>404</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>405</v>
       </c>
       <c r="BC11">
-        <v>0.99653064315884643</v>
+        <v>0.9941446088905187</v>
       </c>
       <c r="BD11">
-        <v>63.604875421149188</v>
+        <v>107.34883700715665</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6635,26 +6764,25 @@
         <v>244</v>
       </c>
       <c r="Y12" t="s">
-        <v>236</v>
-      </c>
-      <c r="Z12" t="str">
-        <f t="shared" ref="Z12:Z30" si="0">"e_sol"&amp;SUBSTITUTE(RIGHT(Y12,2),0,"")</f>
-        <v>e_sol19</v>
+        <v>219</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>285</v>
       </c>
       <c r="AA12">
-        <v>0.99315229827185159</v>
+        <v>0.98911580324852866</v>
       </c>
       <c r="AB12">
-        <v>125.54119834938666</v>
+        <v>199.54360711030768</v>
       </c>
       <c r="AD12" t="s">
         <v>239</v>
       </c>
       <c r="AE12" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AF12" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6669,29 +6797,28 @@
         <v>175</v>
       </c>
       <c r="AL12" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="AM12" t="s">
-        <v>325</v>
-      </c>
-      <c r="AN12" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM12,2),0,"")+20</f>
-        <v>e_won28</v>
+        <v>346</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>347</v>
       </c>
       <c r="AO12">
-        <v>0.98844945266915318</v>
+        <v>0.99498199124719422</v>
       </c>
       <c r="AP12">
-        <v>211.76003439885758</v>
+        <v>91.99682713477273</v>
       </c>
       <c r="AR12" t="s">
         <v>239</v>
       </c>
       <c r="AS12" t="s">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="AT12" t="s">
-        <v>347</v>
+        <v>387</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6706,20 +6833,19 @@
         <v>175</v>
       </c>
       <c r="AZ12" t="s">
-        <v>346</v>
+        <v>386</v>
       </c>
       <c r="BA12" t="s">
-        <v>365</v>
-      </c>
-      <c r="BB12" t="str">
-        <f t="shared" ref="BB12:BB20" si="1">"e_wof"&amp;SUBSTITUTE(RIGHT(BA12,2),0,"")+40</f>
-        <v>e_wof47</v>
+        <v>406</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>407</v>
       </c>
       <c r="BC12">
-        <v>0.99207591869454059</v>
+        <v>0.98954715343009803</v>
       </c>
       <c r="BD12">
-        <v>145.27482393342177</v>
+        <v>191.63552044820315</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6784,26 +6910,25 @@
         <v>246</v>
       </c>
       <c r="Y13" t="s">
-        <v>230</v>
-      </c>
-      <c r="Z13" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol13</v>
+        <v>220</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>286</v>
       </c>
       <c r="AA13">
-        <v>0.98883640519674998</v>
+        <v>0.99356288436829876</v>
       </c>
       <c r="AB13">
-        <v>204.66590472624989</v>
+        <v>118.01378658118981</v>
       </c>
       <c r="AD13" t="s">
         <v>239</v>
       </c>
       <c r="AE13" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="AF13" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -6818,29 +6943,28 @@
         <v>175</v>
       </c>
       <c r="AL13" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="AM13" t="s">
-        <v>326</v>
-      </c>
-      <c r="AN13" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM13,2),0,"")+20</f>
-        <v>e_won33</v>
+        <v>348</v>
+      </c>
+      <c r="AN13" t="s">
+        <v>349</v>
       </c>
       <c r="AO13">
-        <v>0.99427708421681416</v>
+        <v>0.99392750374448113</v>
       </c>
       <c r="AP13">
-        <v>104.92012269174036</v>
+        <v>111.32909801784524</v>
       </c>
       <c r="AR13" t="s">
         <v>239</v>
       </c>
       <c r="AS13" t="s">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="AT13" t="s">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -6855,20 +6979,19 @@
         <v>175</v>
       </c>
       <c r="AZ13" t="s">
-        <v>348</v>
+        <v>388</v>
       </c>
       <c r="BA13" t="s">
-        <v>366</v>
-      </c>
-      <c r="BB13" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof48</v>
+        <v>408</v>
+      </c>
+      <c r="BB13" t="s">
+        <v>409</v>
       </c>
       <c r="BC13">
-        <v>0.98926313025711288</v>
+        <v>0.99204351007823377</v>
       </c>
       <c r="BD13">
-        <v>196.84261195293161</v>
+        <v>145.8689818990471</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -6933,26 +7056,25 @@
         <v>248</v>
       </c>
       <c r="Y14" t="s">
-        <v>225</v>
-      </c>
-      <c r="Z14" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol8</v>
+        <v>221</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>287</v>
       </c>
       <c r="AA14">
-        <v>0.99536570131993762</v>
+        <v>0.99559401474611386</v>
       </c>
       <c r="AB14">
-        <v>84.962142467809898</v>
+        <v>80.776396321244846</v>
       </c>
       <c r="AD14" t="s">
         <v>239</v>
       </c>
       <c r="AE14" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AF14" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -6967,29 +7089,28 @@
         <v>175</v>
       </c>
       <c r="AL14" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AM14" t="s">
-        <v>327</v>
-      </c>
-      <c r="AN14" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM14,2),0,"")+20</f>
-        <v>e_won23</v>
+        <v>350</v>
+      </c>
+      <c r="AN14" t="s">
+        <v>351</v>
       </c>
       <c r="AO14">
-        <v>0.99392750374448113</v>
+        <v>0.98909696821272286</v>
       </c>
       <c r="AP14">
-        <v>111.32909801784524</v>
+        <v>199.88891610008122</v>
       </c>
       <c r="AR14" t="s">
         <v>239</v>
       </c>
       <c r="AS14" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AT14" t="s">
-        <v>351</v>
+        <v>391</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7004,20 +7125,19 @@
         <v>175</v>
       </c>
       <c r="AZ14" t="s">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="BA14" t="s">
-        <v>367</v>
-      </c>
-      <c r="BB14" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof41</v>
+        <v>410</v>
+      </c>
+      <c r="BB14" t="s">
+        <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99136264788907857</v>
+        <v>0.99520217301523817</v>
       </c>
       <c r="BD14">
-        <v>158.35145536689319</v>
+        <v>87.960161387300914</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7082,26 +7202,25 @@
         <v>250</v>
       </c>
       <c r="Y15" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z15" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol3</v>
+        <v>222</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>288</v>
       </c>
       <c r="AA15">
-        <v>0.99356288436829876</v>
+        <v>0.99372835533859694</v>
       </c>
       <c r="AB15">
-        <v>118.01378658118981</v>
+        <v>114.98015212572193</v>
       </c>
       <c r="AD15" t="s">
         <v>239</v>
       </c>
       <c r="AE15" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="AF15" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7116,29 +7235,28 @@
         <v>175</v>
       </c>
       <c r="AL15" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="AM15" t="s">
-        <v>328</v>
-      </c>
-      <c r="AN15" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM15,2),0,"")+20</f>
-        <v>e_won34</v>
+        <v>352</v>
+      </c>
+      <c r="AN15" t="s">
+        <v>353</v>
       </c>
       <c r="AO15">
-        <v>0.99368847580230268</v>
+        <v>0.98751891498768063</v>
       </c>
       <c r="AP15">
-        <v>115.71127695778416</v>
+        <v>228.81989189252232</v>
       </c>
       <c r="AR15" t="s">
         <v>239</v>
       </c>
       <c r="AS15" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AT15" t="s">
-        <v>353</v>
+        <v>393</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7153,20 +7271,19 @@
         <v>175</v>
       </c>
       <c r="AZ15" t="s">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="BA15" t="s">
-        <v>368</v>
-      </c>
-      <c r="BB15" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof44</v>
+        <v>412</v>
+      </c>
+      <c r="BB15" t="s">
+        <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99520217301523817</v>
+        <v>0.99136108064447537</v>
       </c>
       <c r="BD15">
-        <v>87.960161387300914</v>
+        <v>158.38018818461751</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7231,26 +7348,25 @@
         <v>252</v>
       </c>
       <c r="Y16" t="s">
-        <v>233</v>
-      </c>
-      <c r="Z16" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol16</v>
+        <v>223</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>289</v>
       </c>
       <c r="AA16">
-        <v>0.99442875744459613</v>
+        <v>0.990012010348303</v>
       </c>
       <c r="AB16">
-        <v>102.13944684907001</v>
+        <v>183.11314361444599</v>
       </c>
       <c r="AD16" t="s">
         <v>239</v>
       </c>
       <c r="AE16" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="AF16" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7265,29 +7381,28 @@
         <v>175</v>
       </c>
       <c r="AL16" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="AM16" t="s">
-        <v>329</v>
-      </c>
-      <c r="AN16" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM16,2),0,"")+20</f>
-        <v>e_won22</v>
+        <v>354</v>
+      </c>
+      <c r="AN16" t="s">
+        <v>355</v>
       </c>
       <c r="AO16">
-        <v>0.99582677011152854</v>
+        <v>0.99558761976621801</v>
       </c>
       <c r="AP16">
-        <v>76.509214621975957</v>
+        <v>80.893637619336488</v>
       </c>
       <c r="AR16" t="s">
         <v>239</v>
       </c>
       <c r="AS16" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="AT16" t="s">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7302,20 +7417,19 @@
         <v>175</v>
       </c>
       <c r="AZ16" t="s">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="BA16" t="s">
-        <v>369</v>
-      </c>
-      <c r="BB16" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof45</v>
+        <v>414</v>
+      </c>
+      <c r="BB16" t="s">
+        <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99136108064447537</v>
+        <v>0.99653064315884643</v>
       </c>
       <c r="BD16">
-        <v>158.38018818461751</v>
+        <v>63.604875421149188</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7380,26 +7494,25 @@
         <v>254</v>
       </c>
       <c r="Y17" t="s">
-        <v>229</v>
-      </c>
-      <c r="Z17" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol12</v>
+        <v>224</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>290</v>
       </c>
       <c r="AA17">
-        <v>0.99131060083308187</v>
+        <v>0.99371757160137486</v>
       </c>
       <c r="AB17">
-        <v>159.30565139349844</v>
+        <v>115.17785397479503</v>
       </c>
       <c r="AD17" t="s">
         <v>239</v>
       </c>
       <c r="AE17" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="AF17" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7414,29 +7527,28 @@
         <v>175</v>
       </c>
       <c r="AL17" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="AM17" t="s">
-        <v>330</v>
-      </c>
-      <c r="AN17" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM17,2),0,"")+20</f>
-        <v>e_won35</v>
+        <v>356</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>357</v>
       </c>
       <c r="AO17">
-        <v>0.9911442551729287</v>
+        <v>0.99353102787032765</v>
       </c>
       <c r="AP17">
-        <v>162.35532182964019</v>
+        <v>118.59782237732686</v>
       </c>
       <c r="AR17" t="s">
         <v>239</v>
       </c>
       <c r="AS17" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="AT17" t="s">
-        <v>357</v>
+        <v>397</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7451,20 +7563,19 @@
         <v>175</v>
       </c>
       <c r="AZ17" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="BA17" t="s">
-        <v>370</v>
-      </c>
-      <c r="BB17" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof42</v>
+        <v>416</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.98954715343009803</v>
+        <v>0.99207591869454059</v>
       </c>
       <c r="BD17">
-        <v>191.63552044820315</v>
+        <v>145.27482393342177</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7529,26 +7640,25 @@
         <v>256</v>
       </c>
       <c r="Y18" t="s">
-        <v>221</v>
-      </c>
-      <c r="Z18" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol4</v>
+        <v>225</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>291</v>
       </c>
       <c r="AA18">
-        <v>0.99559401474611386</v>
+        <v>0.99536570131993762</v>
       </c>
       <c r="AB18">
-        <v>80.776396321244846</v>
+        <v>84.962142467809898</v>
       </c>
       <c r="AD18" t="s">
         <v>239</v>
       </c>
       <c r="AE18" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="AF18" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7563,29 +7673,28 @@
         <v>175</v>
       </c>
       <c r="AL18" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="AM18" t="s">
-        <v>331</v>
-      </c>
-      <c r="AN18" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM18,2),0,"")+20</f>
-        <v>e_won27</v>
+        <v>358</v>
+      </c>
+      <c r="AN18" t="s">
+        <v>359</v>
       </c>
       <c r="AO18">
-        <v>0.99353102787032765</v>
+        <v>0.98844945266915318</v>
       </c>
       <c r="AP18">
-        <v>118.59782237732686</v>
+        <v>211.76003439885758</v>
       </c>
       <c r="AR18" t="s">
         <v>239</v>
       </c>
       <c r="AS18" t="s">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="AT18" t="s">
-        <v>359</v>
+        <v>399</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7600,20 +7709,19 @@
         <v>175</v>
       </c>
       <c r="AZ18" t="s">
-        <v>358</v>
+        <v>398</v>
       </c>
       <c r="BA18" t="s">
-        <v>371</v>
-      </c>
-      <c r="BB18" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof49</v>
+        <v>418</v>
+      </c>
+      <c r="BB18" t="s">
+        <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.99333526531977001</v>
+        <v>0.98926313025711288</v>
       </c>
       <c r="BD18">
-        <v>122.18680247088278</v>
+        <v>196.84261195293161</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7678,26 +7786,25 @@
         <v>258</v>
       </c>
       <c r="Y19" t="s">
-        <v>232</v>
-      </c>
-      <c r="Z19" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol15</v>
+        <v>226</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>292</v>
       </c>
       <c r="AA19">
-        <v>0.99589633147839685</v>
+        <v>0.98928494645383225</v>
       </c>
       <c r="AB19">
-        <v>75.233922896057891</v>
+        <v>196.44264834640867</v>
       </c>
       <c r="AD19" t="s">
         <v>239</v>
       </c>
       <c r="AE19" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AF19" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -7712,29 +7819,28 @@
         <v>175</v>
       </c>
       <c r="AL19" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AM19" t="s">
-        <v>332</v>
-      </c>
-      <c r="AN19" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM19,2),0,"")+20</f>
-        <v>e_won25</v>
+        <v>360</v>
+      </c>
+      <c r="AN19" t="s">
+        <v>361</v>
       </c>
       <c r="AO19">
-        <v>0.98751891498768063</v>
+        <v>0.99552303355529737</v>
       </c>
       <c r="AP19">
-        <v>228.81989189252232</v>
+        <v>82.077718152882312</v>
       </c>
       <c r="AR19" t="s">
         <v>239</v>
       </c>
       <c r="AS19" t="s">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="AT19" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7749,20 +7855,19 @@
         <v>175</v>
       </c>
       <c r="AZ19" t="s">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="BA19" t="s">
-        <v>372</v>
-      </c>
-      <c r="BB19" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof41</v>
+        <v>420</v>
+      </c>
+      <c r="BB19" t="s">
+        <v>421</v>
       </c>
       <c r="BC19">
-        <v>0.9941446088905187</v>
+        <v>0.99333526531977001</v>
       </c>
       <c r="BD19">
-        <v>107.34883700715665</v>
+        <v>122.18680247088278</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7827,26 +7932,25 @@
         <v>260</v>
       </c>
       <c r="Y20" t="s">
-        <v>237</v>
-      </c>
-      <c r="Z20" t="str">
-        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y20,2),0,"")&amp;"0"</f>
-        <v>e_sol20</v>
+        <v>227</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>293</v>
       </c>
       <c r="AA20">
-        <v>0.9962937079492431</v>
+        <v>0.9866385672597856</v>
       </c>
       <c r="AB20">
-        <v>67.94868759721048</v>
+        <v>244.95960023726295</v>
       </c>
       <c r="AD20" t="s">
         <v>239</v>
       </c>
       <c r="AE20" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="AF20" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -7861,29 +7965,28 @@
         <v>175</v>
       </c>
       <c r="AL20" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="AM20" t="s">
-        <v>333</v>
-      </c>
-      <c r="AN20" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM20,2),0,"")+20</f>
-        <v>e_won31</v>
+        <v>362</v>
+      </c>
+      <c r="AN20" t="s">
+        <v>363</v>
       </c>
       <c r="AO20">
-        <v>0.98768981100926756</v>
+        <v>0.99419279872301636</v>
       </c>
       <c r="AP20">
-        <v>225.68679816342777</v>
+        <v>106.46535674469997</v>
       </c>
       <c r="AR20" t="s">
         <v>239</v>
       </c>
       <c r="AS20" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="AT20" t="s">
-        <v>363</v>
+        <v>403</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -7898,20 +8001,19 @@
         <v>175</v>
       </c>
       <c r="AZ20" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="BA20" t="s">
-        <v>373</v>
-      </c>
-      <c r="BB20" t="str">
-        <f t="shared" si="1"/>
-        <v>e_wof43</v>
+        <v>422</v>
+      </c>
+      <c r="BB20" t="s">
+        <v>423</v>
       </c>
       <c r="BC20">
-        <v>0.99204351007823377</v>
+        <v>0.99136264788907857</v>
       </c>
       <c r="BD20">
-        <v>145.8689818990471</v>
+        <v>158.35145536689319</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -7976,26 +8078,25 @@
         <v>262</v>
       </c>
       <c r="Y21" t="s">
-        <v>224</v>
-      </c>
-      <c r="Z21" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol7</v>
+        <v>228</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>294</v>
       </c>
       <c r="AA21">
-        <v>0.99371757160137486</v>
+        <v>0.98893381891519438</v>
       </c>
       <c r="AB21">
-        <v>115.17785397479503</v>
+        <v>202.87998655476954</v>
       </c>
       <c r="AD21" t="s">
         <v>239</v>
       </c>
       <c r="AE21" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="AF21" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8010,20 +8111,19 @@
         <v>175</v>
       </c>
       <c r="AL21" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="AM21" t="s">
-        <v>334</v>
-      </c>
-      <c r="AN21" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM21,2),0,"")+20</f>
-        <v>e_won21</v>
+        <v>364</v>
+      </c>
+      <c r="AN21" t="s">
+        <v>365</v>
       </c>
       <c r="AO21">
-        <v>0.99419279872301636</v>
+        <v>0.98768981100926756</v>
       </c>
       <c r="AP21">
-        <v>106.46535674469997</v>
+        <v>225.68679816342777</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8088,26 +8188,25 @@
         <v>264</v>
       </c>
       <c r="Y22" t="s">
-        <v>222</v>
-      </c>
-      <c r="Z22" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol5</v>
+        <v>229</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>295</v>
       </c>
       <c r="AA22">
-        <v>0.99372835533859694</v>
+        <v>0.99131060083308187</v>
       </c>
       <c r="AB22">
-        <v>114.98015212572193</v>
+        <v>159.30565139349844</v>
       </c>
       <c r="AD22" t="s">
         <v>239</v>
       </c>
       <c r="AE22" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AF22" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8122,20 +8221,19 @@
         <v>175</v>
       </c>
       <c r="AL22" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AM22" t="s">
-        <v>335</v>
-      </c>
-      <c r="AN22" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM22,2),0,"")+20</f>
-        <v>e_won36</v>
+        <v>366</v>
+      </c>
+      <c r="AN22" t="s">
+        <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99053113122064196</v>
+        <v>0.99436493305946672</v>
       </c>
       <c r="AP22">
-        <v>173.59592762156493</v>
+        <v>103.30956057644399</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8200,26 +8298,25 @@
         <v>266</v>
       </c>
       <c r="Y23" t="s">
-        <v>234</v>
-      </c>
-      <c r="Z23" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol17</v>
+        <v>230</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>296</v>
       </c>
       <c r="AA23">
-        <v>0.9964587744572686</v>
+        <v>0.98883640519674998</v>
       </c>
       <c r="AB23">
-        <v>64.922468283408804</v>
+        <v>204.66590472624989</v>
       </c>
       <c r="AD23" t="s">
         <v>239</v>
       </c>
       <c r="AE23" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="AF23" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8234,20 +8331,19 @@
         <v>175</v>
       </c>
       <c r="AL23" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="AM23" t="s">
-        <v>336</v>
-      </c>
-      <c r="AN23" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM23,2),0,"")+20</f>
-        <v>e_won32</v>
+        <v>368</v>
+      </c>
+      <c r="AN23" t="s">
+        <v>369</v>
       </c>
       <c r="AO23">
-        <v>0.99436493305946672</v>
+        <v>0.99427708421681416</v>
       </c>
       <c r="AP23">
-        <v>103.30956057644399</v>
+        <v>104.92012269174036</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8312,26 +8408,25 @@
         <v>268</v>
       </c>
       <c r="Y24" t="s">
-        <v>235</v>
-      </c>
-      <c r="Z24" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol18</v>
+        <v>231</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>297</v>
       </c>
       <c r="AA24">
-        <v>0.99630851076955973</v>
+        <v>0.99306360188977116</v>
       </c>
       <c r="AB24">
-        <v>67.677302558071602</v>
+        <v>127.16729868752907</v>
       </c>
       <c r="AD24" t="s">
         <v>239</v>
       </c>
       <c r="AE24" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AF24" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8346,20 +8441,19 @@
         <v>175</v>
       </c>
       <c r="AL24" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="AM24" t="s">
-        <v>337</v>
-      </c>
-      <c r="AN24" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM24,2),0,"")+20</f>
-        <v>e_won26</v>
+        <v>370</v>
+      </c>
+      <c r="AN24" t="s">
+        <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99558761976621801</v>
+        <v>0.99368847580230268</v>
       </c>
       <c r="AP24">
-        <v>80.893637619336488</v>
+        <v>115.71127695778416</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8424,26 +8518,25 @@
         <v>270</v>
       </c>
       <c r="Y25" t="s">
-        <v>231</v>
-      </c>
-      <c r="Z25" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol14</v>
+        <v>232</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>298</v>
       </c>
       <c r="AA25">
-        <v>0.99306360188977116</v>
+        <v>0.99589633147839685</v>
       </c>
       <c r="AB25">
-        <v>127.16729868752907</v>
+        <v>75.233922896057891</v>
       </c>
       <c r="AD25" t="s">
         <v>239</v>
       </c>
       <c r="AE25" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="AF25" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8458,20 +8551,19 @@
         <v>175</v>
       </c>
       <c r="AL25" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="AM25" t="s">
-        <v>338</v>
-      </c>
-      <c r="AN25" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM25,2),0,"")+20</f>
-        <v>e_won39</v>
+        <v>372</v>
+      </c>
+      <c r="AN25" t="s">
+        <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.99520787559028878</v>
+        <v>0.9911442551729287</v>
       </c>
       <c r="AP25">
-        <v>87.85561417803892</v>
+        <v>162.35532182964019</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8536,26 +8628,25 @@
         <v>272</v>
       </c>
       <c r="Y26" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z26" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol6</v>
+        <v>233</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>299</v>
       </c>
       <c r="AA26">
-        <v>0.990012010348303</v>
+        <v>0.99442875744459613</v>
       </c>
       <c r="AB26">
-        <v>183.11314361444599</v>
+        <v>102.13944684907001</v>
       </c>
       <c r="AD26" t="s">
         <v>239</v>
       </c>
       <c r="AE26" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="AF26" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -8570,20 +8661,19 @@
         <v>175</v>
       </c>
       <c r="AL26" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="AM26" t="s">
-        <v>339</v>
-      </c>
-      <c r="AN26" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM26,2),0,"")+20</f>
-        <v>e_won29</v>
+        <v>374</v>
+      </c>
+      <c r="AN26" t="s">
+        <v>375</v>
       </c>
       <c r="AO26">
-        <v>0.99552303355529737</v>
+        <v>0.99053113122064196</v>
       </c>
       <c r="AP26">
-        <v>82.077718152882312</v>
+        <v>173.59592762156493</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -8648,26 +8738,25 @@
         <v>274</v>
       </c>
       <c r="Y27" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z27" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol11</v>
+        <v>234</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>300</v>
       </c>
       <c r="AA27">
-        <v>0.98893381891519438</v>
+        <v>0.9964587744572686</v>
       </c>
       <c r="AB27">
-        <v>202.87998655476954</v>
+        <v>64.922468283408804</v>
       </c>
       <c r="AD27" t="s">
         <v>239</v>
       </c>
       <c r="AE27" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="AF27" t="s">
-        <v>317</v>
+        <v>337</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -8682,14 +8771,13 @@
         <v>175</v>
       </c>
       <c r="AL27" t="s">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="AM27" t="s">
-        <v>340</v>
-      </c>
-      <c r="AN27" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM27,2),0,"")+20</f>
-        <v>e_won37</v>
+        <v>376</v>
+      </c>
+      <c r="AN27" t="s">
+        <v>377</v>
       </c>
       <c r="AO27">
         <v>0.9913766042890243</v>
@@ -8760,26 +8848,25 @@
         <v>276</v>
       </c>
       <c r="Y28" t="s">
-        <v>227</v>
-      </c>
-      <c r="Z28" t="str">
-        <f>"e_sol"&amp;SUBSTITUTE(RIGHT(Y28,2),0,"")&amp;"0"</f>
-        <v>e_sol10</v>
+        <v>235</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>301</v>
       </c>
       <c r="AA28">
-        <v>0.9866385672597856</v>
+        <v>0.99630851076955973</v>
       </c>
       <c r="AB28">
-        <v>244.95960023726295</v>
+        <v>67.677302558071602</v>
       </c>
       <c r="AD28" t="s">
         <v>239</v>
       </c>
       <c r="AE28" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="AF28" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -8794,20 +8881,19 @@
         <v>175</v>
       </c>
       <c r="AL28" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="AM28" t="s">
-        <v>341</v>
-      </c>
-      <c r="AN28" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM28,2),0,"")+20</f>
-        <v>e_won22</v>
+        <v>378</v>
+      </c>
+      <c r="AN28" t="s">
+        <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.99498199124719422</v>
+        <v>0.98926286248458195</v>
       </c>
       <c r="AP28">
-        <v>91.99682713477273</v>
+        <v>196.84752111599829</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8872,26 +8958,25 @@
         <v>278</v>
       </c>
       <c r="Y29" t="s">
-        <v>226</v>
-      </c>
-      <c r="Z29" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol9</v>
+        <v>236</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>302</v>
       </c>
       <c r="AA29">
-        <v>0.98928494645383225</v>
+        <v>0.99315229827185159</v>
       </c>
       <c r="AB29">
-        <v>196.44264834640867</v>
+        <v>125.54119834938666</v>
       </c>
       <c r="AD29" t="s">
         <v>239</v>
       </c>
       <c r="AE29" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AF29" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -8906,20 +8991,19 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s">
-        <v>320</v>
+        <v>340</v>
       </c>
       <c r="AM29" t="s">
-        <v>342</v>
-      </c>
-      <c r="AN29" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM29,2),0,"")+20</f>
-        <v>e_won38</v>
+        <v>380</v>
+      </c>
+      <c r="AN29" t="s">
+        <v>381</v>
       </c>
       <c r="AO29">
-        <v>0.98926286248458195</v>
+        <v>0.99520787559028878</v>
       </c>
       <c r="AP29">
-        <v>196.84752111599829</v>
+        <v>87.85561417803892</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -8984,26 +9068,25 @@
         <v>280</v>
       </c>
       <c r="Y30" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z30" t="str">
-        <f t="shared" si="0"/>
-        <v>e_sol1</v>
+        <v>237</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>303</v>
       </c>
       <c r="AA30">
-        <v>0.9905299918588647</v>
+        <v>0.9962937079492431</v>
       </c>
       <c r="AB30">
-        <v>173.61681592081291</v>
+        <v>67.94868759721048</v>
       </c>
       <c r="AD30" t="s">
         <v>239</v>
       </c>
       <c r="AE30" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="AF30" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -9018,20 +9101,19 @@
         <v>175</v>
       </c>
       <c r="AL30" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="AM30" t="s">
-        <v>343</v>
-      </c>
-      <c r="AN30" t="str">
-        <f>"e_won"&amp;SUBSTITUTE(RIGHT(AM30,2),0,"")+20</f>
-        <v>e_won24</v>
+        <v>382</v>
+      </c>
+      <c r="AN30" t="s">
+        <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.98909696821272286</v>
+        <v>0.99582677011152854</v>
       </c>
       <c r="AP30">
-        <v>199.88891610008122</v>
+        <v>76.509214621975957</v>
       </c>
     </row>
   </sheetData>
@@ -9040,7 +9122,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C42831-07FE-4634-97C7-7A0755AD8A77}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96499DCA-62FD-471F-B805-9B62C59E7A36}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9131,10 +9213,10 @@
         <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="D11" t="s">
-        <v>375</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9149,10 +9231,10 @@
         <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>374</v>
+        <v>424</v>
       </c>
       <c r="K11" t="s">
-        <v>324</v>
+        <v>344</v>
       </c>
       <c r="L11">
         <v>0.45167200935612223</v>
@@ -9164,10 +9246,10 @@
         <v>171</v>
       </c>
       <c r="P11" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="Q11" t="s">
-        <v>415</v>
+        <v>465</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9182,10 +9264,10 @@
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>414</v>
+        <v>464</v>
       </c>
       <c r="X11" t="s">
-        <v>372</v>
+        <v>404</v>
       </c>
       <c r="Y11">
         <v>0.83925000000000005</v>
@@ -9199,10 +9281,10 @@
         <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="D12" t="s">
-        <v>377</v>
+        <v>427</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9217,10 +9299,10 @@
         <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>376</v>
+        <v>426</v>
       </c>
       <c r="K12" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="L12">
         <v>0.50504353376491207</v>
@@ -9232,10 +9314,10 @@
         <v>171</v>
       </c>
       <c r="P12" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="Q12" t="s">
-        <v>417</v>
+        <v>467</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9250,10 +9332,10 @@
         <v>175</v>
       </c>
       <c r="W12" t="s">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="X12" t="s">
-        <v>370</v>
+        <v>406</v>
       </c>
       <c r="Y12">
         <v>16.887</v>
@@ -9267,10 +9349,10 @@
         <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="D13" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -9285,10 +9367,10 @@
         <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>378</v>
+        <v>428</v>
       </c>
       <c r="K13" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="L13">
         <v>1.7897871713950226</v>
@@ -9300,10 +9382,10 @@
         <v>171</v>
       </c>
       <c r="P13" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="Q13" t="s">
-        <v>419</v>
+        <v>469</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -9318,10 +9400,10 @@
         <v>175</v>
       </c>
       <c r="W13" t="s">
-        <v>418</v>
+        <v>468</v>
       </c>
       <c r="X13" t="s">
-        <v>373</v>
+        <v>408</v>
       </c>
       <c r="Y13">
         <v>11.2965</v>
@@ -9335,10 +9417,10 @@
         <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="D14" t="s">
-        <v>381</v>
+        <v>431</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -9353,10 +9435,10 @@
         <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="K14" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="L14">
         <v>2.6804732670444085</v>
@@ -9368,10 +9450,10 @@
         <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="Q14" t="s">
-        <v>421</v>
+        <v>471</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -9386,10 +9468,10 @@
         <v>175</v>
       </c>
       <c r="W14" t="s">
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="X14" t="s">
-        <v>368</v>
+        <v>410</v>
       </c>
       <c r="Y14">
         <v>6.6577500000000001</v>
@@ -9403,10 +9485,10 @@
         <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="D15" t="s">
-        <v>383</v>
+        <v>433</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -9421,10 +9503,10 @@
         <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="K15" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="L15">
         <v>8.0517810049421517</v>
@@ -9436,10 +9518,10 @@
         <v>171</v>
       </c>
       <c r="P15" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="Q15" t="s">
-        <v>423</v>
+        <v>473</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -9454,10 +9536,10 @@
         <v>175</v>
       </c>
       <c r="W15" t="s">
-        <v>422</v>
+        <v>472</v>
       </c>
       <c r="X15" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="Y15">
         <v>17.089500000000001</v>
@@ -9471,10 +9553,10 @@
         <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="D16" t="s">
-        <v>385</v>
+        <v>435</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -9489,10 +9571,10 @@
         <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>384</v>
+        <v>434</v>
       </c>
       <c r="K16" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="L16">
         <v>0.96273897344398884</v>
@@ -9504,10 +9586,10 @@
         <v>171</v>
       </c>
       <c r="P16" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="Q16" t="s">
-        <v>425</v>
+        <v>475</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -9522,10 +9604,10 @@
         <v>175</v>
       </c>
       <c r="W16" t="s">
-        <v>424</v>
+        <v>474</v>
       </c>
       <c r="X16" t="s">
-        <v>364</v>
+        <v>414</v>
       </c>
       <c r="Y16">
         <v>10.023</v>
@@ -9539,10 +9621,10 @@
         <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="D17" t="s">
-        <v>387</v>
+        <v>437</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -9557,10 +9639,10 @@
         <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>386</v>
+        <v>436</v>
       </c>
       <c r="K17" t="s">
-        <v>331</v>
+        <v>356</v>
       </c>
       <c r="L17">
         <v>1.093890418371007</v>
@@ -9572,10 +9654,10 @@
         <v>171</v>
       </c>
       <c r="P17" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="Q17" t="s">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -9590,10 +9672,10 @@
         <v>175</v>
       </c>
       <c r="W17" t="s">
-        <v>426</v>
+        <v>476</v>
       </c>
       <c r="X17" t="s">
-        <v>365</v>
+        <v>416</v>
       </c>
       <c r="Y17">
         <v>0.22650000000000001</v>
@@ -9607,10 +9689,10 @@
         <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="D18" t="s">
-        <v>389</v>
+        <v>439</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -9625,10 +9707,10 @@
         <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>388</v>
+        <v>438</v>
       </c>
       <c r="K18" t="s">
-        <v>325</v>
+        <v>358</v>
       </c>
       <c r="L18">
         <v>3.1665724666245323</v>
@@ -9640,10 +9722,10 @@
         <v>171</v>
       </c>
       <c r="P18" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="Q18" t="s">
-        <v>429</v>
+        <v>479</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -9658,10 +9740,10 @@
         <v>175</v>
       </c>
       <c r="W18" t="s">
-        <v>428</v>
+        <v>478</v>
       </c>
       <c r="X18" t="s">
-        <v>366</v>
+        <v>418</v>
       </c>
       <c r="Y18">
         <v>9.5062499999999996</v>
@@ -9675,10 +9757,10 @@
         <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="D19" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -9693,10 +9775,10 @@
         <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="K19" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="L19">
         <v>0.55491188155257321</v>
@@ -9708,10 +9790,10 @@
         <v>171</v>
       </c>
       <c r="P19" t="s">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="Q19" t="s">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -9726,10 +9808,10 @@
         <v>175</v>
       </c>
       <c r="W19" t="s">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="X19" t="s">
-        <v>371</v>
+        <v>420</v>
       </c>
       <c r="Y19">
         <v>13.37175</v>
@@ -9743,10 +9825,10 @@
         <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="D20" t="s">
-        <v>393</v>
+        <v>443</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -9761,10 +9843,10 @@
         <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="K20" t="s">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="L20">
         <v>0.97886072674627833</v>
@@ -9776,10 +9858,10 @@
         <v>171</v>
       </c>
       <c r="P20" t="s">
-        <v>432</v>
+        <v>482</v>
       </c>
       <c r="Q20" t="s">
-        <v>433</v>
+        <v>483</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -9794,10 +9876,10 @@
         <v>175</v>
       </c>
       <c r="W20" t="s">
-        <v>432</v>
+        <v>482</v>
       </c>
       <c r="X20" t="s">
-        <v>367</v>
+        <v>422</v>
       </c>
       <c r="Y20">
         <v>3.9427500000000002</v>
@@ -9811,10 +9893,10 @@
         <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="D21" t="s">
-        <v>395</v>
+        <v>445</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -9829,10 +9911,10 @@
         <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>394</v>
+        <v>444</v>
       </c>
       <c r="K21" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="L21">
         <v>0.40593208719379742</v>
@@ -9846,10 +9928,10 @@
         <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="D22" t="s">
-        <v>397</v>
+        <v>447</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -9864,10 +9946,10 @@
         <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>396</v>
+        <v>446</v>
       </c>
       <c r="K22" t="s">
-        <v>336</v>
+        <v>366</v>
       </c>
       <c r="L22">
         <v>0.8833561507867439</v>
@@ -9881,10 +9963,10 @@
         <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="D23" t="s">
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -9899,10 +9981,10 @@
         <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>398</v>
+        <v>448</v>
       </c>
       <c r="K23" t="s">
-        <v>326</v>
+        <v>368</v>
       </c>
       <c r="L23">
         <v>0.40306698622644632</v>
@@ -9916,10 +9998,10 @@
         <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="D24" t="s">
-        <v>401</v>
+        <v>451</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -9934,10 +10016,10 @@
         <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="K24" t="s">
-        <v>328</v>
+        <v>370</v>
       </c>
       <c r="L24">
         <v>0.84020182400735144</v>
@@ -9951,10 +10033,10 @@
         <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="D25" t="s">
-        <v>403</v>
+        <v>453</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -9969,10 +10051,10 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>402</v>
+        <v>452</v>
       </c>
       <c r="K25" t="s">
-        <v>330</v>
+        <v>372</v>
       </c>
       <c r="L25">
         <v>0.35328950844501877</v>
@@ -9986,10 +10068,10 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="D26" t="s">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -10004,10 +10086,10 @@
         <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>404</v>
+        <v>454</v>
       </c>
       <c r="K26" t="s">
-        <v>335</v>
+        <v>374</v>
       </c>
       <c r="L26">
         <v>0.89446396558783758</v>
@@ -10021,10 +10103,10 @@
         <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="D27" t="s">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -10039,10 +10121,10 @@
         <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>406</v>
+        <v>456</v>
       </c>
       <c r="K27" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="L27">
         <v>0.55411362221124194</v>
@@ -10056,10 +10138,10 @@
         <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="D28" t="s">
-        <v>409</v>
+        <v>459</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -10074,10 +10156,10 @@
         <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>408</v>
+        <v>458</v>
       </c>
       <c r="K28" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="L28">
         <v>1.4637274230737423</v>
@@ -10091,10 +10173,10 @@
         <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="D29" t="s">
-        <v>411</v>
+        <v>461</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -10109,10 +10191,10 @@
         <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>410</v>
+        <v>460</v>
       </c>
       <c r="K29" t="s">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="L29">
         <v>0.63042801517356961</v>
@@ -10126,10 +10208,10 @@
         <v>171</v>
       </c>
       <c r="C30" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="D30" t="s">
-        <v>413</v>
+        <v>463</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -10144,10 +10226,10 @@
         <v>175</v>
       </c>
       <c r="J30" t="s">
-        <v>412</v>
+        <v>462</v>
       </c>
       <c r="K30" t="s">
-        <v>329</v>
+        <v>382</v>
       </c>
       <c r="L30">
         <v>0.61343702722931326</v>
@@ -10162,7 +10244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA3B521F-A299-4E3E-A0D7-74FB2DA968BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A27BD33-11D2-434B-AF45-C003801F201A}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10220,7 +10302,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -10244,7 +10326,7 @@
         <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -10256,12 +10338,12 @@
         <v>243</v>
       </c>
       <c r="P11" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -10279,13 +10361,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
       <c r="J12" t="s">
         <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -10297,12 +10379,12 @@
         <v>243</v>
       </c>
       <c r="P12" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -10320,13 +10402,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="J13" t="s">
         <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -10338,12 +10420,12 @@
         <v>243</v>
       </c>
       <c r="P13" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -10361,13 +10443,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
       <c r="J14" t="s">
         <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -10379,12 +10461,12 @@
         <v>243</v>
       </c>
       <c r="P14" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>434</v>
+        <v>484</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -10402,13 +10484,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
       <c r="J15" t="s">
         <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -10420,12 +10502,12 @@
         <v>243</v>
       </c>
       <c r="P15" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -10449,7 +10531,7 @@
         <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -10461,12 +10543,12 @@
         <v>243</v>
       </c>
       <c r="P16" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -10484,13 +10566,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
       <c r="J17" t="s">
         <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -10502,12 +10584,12 @@
         <v>243</v>
       </c>
       <c r="P17" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -10525,13 +10607,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="J18" t="s">
         <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -10543,12 +10625,12 @@
         <v>243</v>
       </c>
       <c r="P18" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -10566,13 +10648,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -10584,12 +10666,12 @@
         <v>243</v>
       </c>
       <c r="P19" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -10607,13 +10689,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
       <c r="J20" t="s">
         <v>171</v>
       </c>
       <c r="K20" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -10625,12 +10707,12 @@
         <v>243</v>
       </c>
       <c r="P20" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -10654,7 +10736,7 @@
         <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -10666,12 +10748,12 @@
         <v>243</v>
       </c>
       <c r="P21" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -10689,13 +10771,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="J22" t="s">
         <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -10707,12 +10789,12 @@
         <v>243</v>
       </c>
       <c r="P22" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>440</v>
+        <v>490</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -10730,13 +10812,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
       <c r="J23" t="s">
         <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -10748,12 +10830,12 @@
         <v>243</v>
       </c>
       <c r="P23" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -10777,7 +10859,7 @@
         <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -10789,12 +10871,12 @@
         <v>243</v>
       </c>
       <c r="P24" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -10812,13 +10894,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
       <c r="J25" t="s">
         <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -10830,12 +10912,12 @@
         <v>243</v>
       </c>
       <c r="P25" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>441</v>
+        <v>491</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -10853,13 +10935,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
       <c r="J26" t="s">
         <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -10871,12 +10953,12 @@
         <v>243</v>
       </c>
       <c r="P26" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -10900,7 +10982,7 @@
         <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -10912,12 +10994,12 @@
         <v>243</v>
       </c>
       <c r="P27" t="s">
-        <v>456</v>
+        <v>506</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -10935,12 +11017,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>442</v>
+        <v>492</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -10958,12 +11040,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -10986,7 +11068,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -11004,12 +11086,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>443</v>
+        <v>493</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -11027,12 +11109,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -11055,7 +11137,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -11073,12 +11155,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -11096,12 +11178,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -11119,12 +11201,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -11142,12 +11224,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -11170,7 +11252,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -11188,12 +11270,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>445</v>
+        <v>495</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -11211,12 +11293,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -11239,7 +11321,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -11257,12 +11339,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>446</v>
+        <v>496</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -11280,12 +11362,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -11308,7 +11390,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -11326,12 +11408,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -11349,12 +11431,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -11377,7 +11459,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -11395,12 +11477,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>448</v>
+        <v>498</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -11418,12 +11500,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -11446,7 +11528,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -11464,12 +11546,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -11487,12 +11569,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -11510,12 +11592,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>449</v>
+        <v>499</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -11533,12 +11615,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -11561,7 +11643,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -11579,12 +11661,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -11602,12 +11684,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -11630,7 +11712,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -11648,12 +11730,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>451</v>
+        <v>501</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -11671,12 +11753,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -11699,7 +11781,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -11717,12 +11799,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>452</v>
+        <v>502</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -11740,15 +11822,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="C64" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -11768,10 +11850,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="C65" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -11786,15 +11868,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="C66" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -11809,15 +11891,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -11832,15 +11914,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>453</v>
+        <v>503</v>
       </c>
       <c r="C68" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -11855,15 +11937,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C69" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -11883,10 +11965,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C70" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -11901,15 +11983,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>435</v>
+        <v>485</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C71" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -11924,15 +12006,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>436</v>
+        <v>486</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C72" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -11947,15 +12029,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>437</v>
+        <v>487</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>455</v>
+        <v>505</v>
       </c>
       <c r="C73" t="s">
-        <v>454</v>
+        <v>504</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -11970,7 +12052,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>438</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{582EE015-2889-4C4F-9D6D-1B7EDFA6F16D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44319431-2D06-4368-A4E5-A173CD0F7372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6380,7 +6380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D3F9912-AEDE-4DAE-BE1C-3A1E3CF1C745}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880ADF8B-E6E6-4D96-AA65-AC351F2375C2}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6624,10 +6624,10 @@
         <v>284</v>
       </c>
       <c r="AA11">
-        <v>0.9905299918588647</v>
+        <v>0.99052511709569879</v>
       </c>
       <c r="AB11">
-        <v>173.61681592081291</v>
+        <v>173.7061865788562</v>
       </c>
       <c r="AD11" t="s">
         <v>239</v>
@@ -6660,10 +6660,10 @@
         <v>345</v>
       </c>
       <c r="AO11">
-        <v>0.99363378101904942</v>
+        <v>0.99363266304217013</v>
       </c>
       <c r="AP11">
-        <v>116.71401465075998</v>
+        <v>116.73451089354681</v>
       </c>
       <c r="AR11" t="s">
         <v>239</v>
@@ -6770,10 +6770,10 @@
         <v>285</v>
       </c>
       <c r="AA12">
-        <v>0.98911580324852866</v>
+        <v>0.98930442340690594</v>
       </c>
       <c r="AB12">
-        <v>199.54360711030768</v>
+        <v>196.08557087339125</v>
       </c>
       <c r="AD12" t="s">
         <v>239</v>
@@ -6806,10 +6806,10 @@
         <v>347</v>
       </c>
       <c r="AO12">
-        <v>0.99498199124719422</v>
+        <v>0.99503406068424616</v>
       </c>
       <c r="AP12">
-        <v>91.99682713477273</v>
+        <v>91.042220788820273</v>
       </c>
       <c r="AR12" t="s">
         <v>239</v>
@@ -6916,10 +6916,10 @@
         <v>286</v>
       </c>
       <c r="AA13">
-        <v>0.99356288436829876</v>
+        <v>0.99359298789982198</v>
       </c>
       <c r="AB13">
-        <v>118.01378658118981</v>
+        <v>117.46188850326349</v>
       </c>
       <c r="AD13" t="s">
         <v>239</v>
@@ -6952,10 +6952,10 @@
         <v>349</v>
       </c>
       <c r="AO13">
-        <v>0.99392750374448113</v>
+        <v>0.99376233652729562</v>
       </c>
       <c r="AP13">
-        <v>111.32909801784524</v>
+        <v>114.35716366624744</v>
       </c>
       <c r="AR13" t="s">
         <v>239</v>
@@ -7062,10 +7062,10 @@
         <v>287</v>
       </c>
       <c r="AA14">
-        <v>0.99559401474611386</v>
+        <v>0.99559202148411841</v>
       </c>
       <c r="AB14">
-        <v>80.776396321244846</v>
+        <v>80.812939457829899</v>
       </c>
       <c r="AD14" t="s">
         <v>239</v>
@@ -7134,10 +7134,10 @@
         <v>411</v>
       </c>
       <c r="BC14">
-        <v>0.99520217301523817</v>
+        <v>0.99531556489563333</v>
       </c>
       <c r="BD14">
-        <v>87.960161387300914</v>
+        <v>85.881310246721398</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7208,10 +7208,10 @@
         <v>288</v>
       </c>
       <c r="AA15">
-        <v>0.99372835533859694</v>
+        <v>0.99372560828751888</v>
       </c>
       <c r="AB15">
-        <v>114.98015212572193</v>
+        <v>115.03051472881981</v>
       </c>
       <c r="AD15" t="s">
         <v>239</v>
@@ -7244,10 +7244,10 @@
         <v>353</v>
       </c>
       <c r="AO15">
-        <v>0.98751891498768063</v>
+        <v>0.98748716330994268</v>
       </c>
       <c r="AP15">
-        <v>228.81989189252232</v>
+        <v>229.40200598438332</v>
       </c>
       <c r="AR15" t="s">
         <v>239</v>
@@ -7280,10 +7280,10 @@
         <v>413</v>
       </c>
       <c r="BC15">
-        <v>0.99136108064447537</v>
+        <v>0.99126367634007251</v>
       </c>
       <c r="BD15">
-        <v>158.38018818461751</v>
+        <v>160.16593376533709</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7390,10 +7390,10 @@
         <v>355</v>
       </c>
       <c r="AO16">
-        <v>0.99558761976621801</v>
+        <v>0.99544898335172294</v>
       </c>
       <c r="AP16">
-        <v>80.893637619336488</v>
+        <v>83.435305218412225</v>
       </c>
       <c r="AR16" t="s">
         <v>239</v>
@@ -7426,10 +7426,10 @@
         <v>415</v>
       </c>
       <c r="BC16">
-        <v>0.99653064315884643</v>
+        <v>0.9964252974188933</v>
       </c>
       <c r="BD16">
-        <v>63.604875421149188</v>
+        <v>65.536213986956668</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7500,10 +7500,10 @@
         <v>290</v>
       </c>
       <c r="AA17">
-        <v>0.99371757160137486</v>
+        <v>0.99369398178107105</v>
       </c>
       <c r="AB17">
-        <v>115.17785397479503</v>
+        <v>115.61033401369787</v>
       </c>
       <c r="AD17" t="s">
         <v>239</v>
@@ -7572,10 +7572,10 @@
         <v>417</v>
       </c>
       <c r="BC17">
-        <v>0.99207591869454059</v>
+        <v>0.99210017397898553</v>
       </c>
       <c r="BD17">
-        <v>145.27482393342177</v>
+        <v>144.8301437185994</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7718,10 +7718,10 @@
         <v>419</v>
       </c>
       <c r="BC18">
-        <v>0.98926313025711288</v>
+        <v>0.9892917933303903</v>
       </c>
       <c r="BD18">
-        <v>196.84261195293161</v>
+        <v>196.31712227617862</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7792,10 +7792,10 @@
         <v>292</v>
       </c>
       <c r="AA19">
-        <v>0.98928494645383225</v>
+        <v>0.98904170636947841</v>
       </c>
       <c r="AB19">
-        <v>196.44264834640867</v>
+        <v>200.90204989289663</v>
       </c>
       <c r="AD19" t="s">
         <v>239</v>
@@ -7864,10 +7864,10 @@
         <v>421</v>
       </c>
       <c r="BC19">
-        <v>0.99333526531977001</v>
+        <v>0.99349205504215798</v>
       </c>
       <c r="BD19">
-        <v>122.18680247088278</v>
+        <v>119.31232422710414</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -7974,10 +7974,10 @@
         <v>363</v>
       </c>
       <c r="AO20">
-        <v>0.99419279872301636</v>
+        <v>0.99418970404065432</v>
       </c>
       <c r="AP20">
-        <v>106.46535674469997</v>
+        <v>106.52209258800498</v>
       </c>
       <c r="AR20" t="s">
         <v>239</v>
@@ -8010,10 +8010,10 @@
         <v>423</v>
       </c>
       <c r="BC20">
-        <v>0.99136264788907857</v>
+        <v>0.99148653509417994</v>
       </c>
       <c r="BD20">
-        <v>158.35145536689319</v>
+        <v>156.08018994003498</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8230,10 +8230,10 @@
         <v>367</v>
       </c>
       <c r="AO22">
-        <v>0.99436493305946672</v>
+        <v>0.99435161378360182</v>
       </c>
       <c r="AP22">
-        <v>103.30956057644399</v>
+        <v>103.55374730063295</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8304,10 +8304,10 @@
         <v>296</v>
       </c>
       <c r="AA23">
-        <v>0.98883640519674998</v>
+        <v>0.98882091423845997</v>
       </c>
       <c r="AB23">
-        <v>204.66590472624989</v>
+        <v>204.94990562823315</v>
       </c>
       <c r="AD23" t="s">
         <v>239</v>
@@ -8414,10 +8414,10 @@
         <v>297</v>
       </c>
       <c r="AA24">
-        <v>0.99306360188977116</v>
+        <v>0.99306125367810116</v>
       </c>
       <c r="AB24">
-        <v>127.16729868752907</v>
+        <v>127.21034923481231</v>
       </c>
       <c r="AD24" t="s">
         <v>239</v>
@@ -8450,10 +8450,10 @@
         <v>371</v>
       </c>
       <c r="AO24">
-        <v>0.99368847580230268</v>
+        <v>0.99368608205177045</v>
       </c>
       <c r="AP24">
-        <v>115.71127695778416</v>
+        <v>115.75516238420887</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8524,10 +8524,10 @@
         <v>298</v>
       </c>
       <c r="AA25">
-        <v>0.99589633147839685</v>
+        <v>0.99594031040905284</v>
       </c>
       <c r="AB25">
-        <v>75.233922896057891</v>
+        <v>74.427642500698539</v>
       </c>
       <c r="AD25" t="s">
         <v>239</v>
@@ -8560,10 +8560,10 @@
         <v>373</v>
       </c>
       <c r="AO25">
-        <v>0.9911442551729287</v>
+        <v>0.99113070337008702</v>
       </c>
       <c r="AP25">
-        <v>162.35532182964019</v>
+        <v>162.60377154840413</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8634,10 +8634,10 @@
         <v>299</v>
       </c>
       <c r="AA26">
-        <v>0.99442875744459613</v>
+        <v>0.99416798014777663</v>
       </c>
       <c r="AB26">
-        <v>102.13944684907001</v>
+        <v>106.92036395742902</v>
       </c>
       <c r="AD26" t="s">
         <v>239</v>
@@ -8744,10 +8744,10 @@
         <v>300</v>
       </c>
       <c r="AA27">
-        <v>0.9964587744572686</v>
+        <v>0.99645066092519663</v>
       </c>
       <c r="AB27">
-        <v>64.922468283408804</v>
+        <v>65.071216371396105</v>
       </c>
       <c r="AD27" t="s">
         <v>239</v>
@@ -8890,10 +8890,10 @@
         <v>379</v>
       </c>
       <c r="AO28">
-        <v>0.98926286248458195</v>
+        <v>0.98943796188704269</v>
       </c>
       <c r="AP28">
-        <v>196.84752111599829</v>
+        <v>193.63736540421718</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -8964,10 +8964,10 @@
         <v>302</v>
       </c>
       <c r="AA29">
-        <v>0.99315229827185159</v>
+        <v>0.99330696849324529</v>
       </c>
       <c r="AB29">
-        <v>125.54119834938666</v>
+        <v>122.70557762383625</v>
       </c>
       <c r="AD29" t="s">
         <v>239</v>
@@ -9074,10 +9074,10 @@
         <v>303</v>
       </c>
       <c r="AA30">
-        <v>0.9962937079492431</v>
+        <v>0.99605762638605078</v>
       </c>
       <c r="AB30">
-        <v>67.94868759721048</v>
+        <v>72.276849589069343</v>
       </c>
       <c r="AD30" t="s">
         <v>239</v>
@@ -9110,10 +9110,10 @@
         <v>383</v>
       </c>
       <c r="AO30">
-        <v>0.99582677011152854</v>
+        <v>0.99589853466628631</v>
       </c>
       <c r="AP30">
-        <v>76.509214621975957</v>
+        <v>75.193531118084408</v>
       </c>
     </row>
   </sheetData>
@@ -9122,7 +9122,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96499DCA-62FD-471F-B805-9B62C59E7A36}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA97C79-9FEB-49D2-9121-CF2603EF205E}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10244,7 +10244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A27BD33-11D2-434B-AF45-C003801F201A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79C7430-0825-421C-8778-EBC6B8321523}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44319431-2D06-4368-A4E5-A173CD0F7372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{532228EB-B68A-4EAF-8091-AADA380E71DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6380,7 +6380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{880ADF8B-E6E6-4D96-AA65-AC351F2375C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F409D21-F894-4E43-94CB-CA3335967354}">
   <dimension ref="B9:BD30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9122,7 +9122,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA97C79-9FEB-49D2-9121-CF2603EF205E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3E748B-1078-4419-A138-C9487B7F2AFE}">
   <dimension ref="B9:Z30"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10244,7 +10244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A79C7430-0825-421C-8778-EBC6B8321523}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F658A0AE-515E-428A-86C3-71844977F562}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
